--- a/shipping-tool/document/範例產出檔案.xlsx
+++ b/shipping-tool/document/範例產出檔案.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\RondoFile\客戶\巨瑞國際\source\SI自動化產製\shipping-tool\document\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\RondoFile\客戶\巨瑞國際\source\SIReport_Auto\shipping-tool\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EC3A8C8-8446-4211-9A8B-A164EA796F7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8486B5D-D166-4AE3-8127-2C4C41DDB56F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="35640" yWindow="360" windowWidth="15030" windowHeight="15540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1152" yWindow="756" windowWidth="14304" windowHeight="12204" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SI " sheetId="35" r:id="rId1"/>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="185">
   <si>
     <t>CTNS</t>
   </si>
@@ -1035,18 +1035,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="細明體"/>
-        <family val="3"/>
-        <charset val="136"/>
-      </rPr>
-      <t>併櫃工廠</t>
-    </r>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <r>
       <t xml:space="preserve">FWD </t>
     </r>
     <r>
@@ -1081,10 +1069,6 @@
       </rPr>
       <t>負責報關</t>
     </r>
-  </si>
-  <si>
-    <t>MEN'S FOOTWEAR</t>
-    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <t>PI#</t>
@@ -1163,7 +1147,7 @@
     <numFmt numFmtId="184" formatCode="_-&quot;$&quot;* #,##0.00_-;&quot;-$&quot;* #,##0.00_-;_-&quot;$&quot;* \-??_-;_-@_-"/>
     <numFmt numFmtId="185" formatCode="0.00_ "/>
   </numFmts>
-  <fonts count="53">
+  <fonts count="54">
     <font>
       <sz val="12"/>
       <name val="新細明體"/>
@@ -1489,6 +1473,13 @@
       <b/>
       <sz val="11"/>
       <name val="Microsoft JhengHei"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Microsoft JhengHei"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="4">
@@ -2381,15 +2372,48 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="10" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="37" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="37" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="37" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="3" borderId="0" xfId="37" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="37" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="0" xfId="93" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="37" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="14" fillId="3" borderId="0" xfId="37" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="14" fillId="3" borderId="0" xfId="37" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="0" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="3" borderId="0" xfId="37" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="36" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="22" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="22" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="36" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="18" fillId="2" borderId="1" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
@@ -2477,41 +2501,8 @@
     <xf numFmtId="0" fontId="50" fillId="0" borderId="1" xfId="46" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="37" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="37" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="37" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="6" xfId="44" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="37" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="3" borderId="0" xfId="37" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="37" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="0" xfId="93" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="37" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="14" fillId="3" borderId="0" xfId="37" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="14" fillId="3" borderId="0" xfId="37" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="0" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="3" borderId="0" xfId="37" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="98">
@@ -2975,25 +2966,25 @@
     <col min="1005" max="16384" width="8.88671875" style="35"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="4" customFormat="1" ht="21">
-      <c r="A1" s="148" t="s">
+    <row r="1" spans="1:10" s="4" customFormat="1" ht="21">
+      <c r="A1" s="157" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="148"/>
-      <c r="C1" s="148"/>
-      <c r="D1" s="148"/>
-      <c r="E1" s="148"/>
-      <c r="F1" s="148"/>
-      <c r="G1" s="148"/>
+      <c r="B1" s="157"/>
+      <c r="C1" s="157"/>
+      <c r="D1" s="157"/>
+      <c r="E1" s="157"/>
+      <c r="F1" s="157"/>
+      <c r="G1" s="157"/>
       <c r="H1" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I1" s="2" t="s">
         <v>119</v>
       </c>
       <c r="J1" s="3"/>
     </row>
-    <row r="2" spans="1:12" s="4" customFormat="1" ht="13.2" customHeight="1">
+    <row r="2" spans="1:10" s="4" customFormat="1" ht="13.2" customHeight="1">
       <c r="A2" s="75"/>
       <c r="B2" s="75"/>
       <c r="C2" s="75"/>
@@ -3005,7 +2996,7 @@
       <c r="I2" s="2"/>
       <c r="J2" s="3"/>
     </row>
-    <row r="3" spans="1:12" s="6" customFormat="1" ht="15">
+    <row r="3" spans="1:10" s="6" customFormat="1" ht="15">
       <c r="A3" s="5" t="s">
         <v>117</v>
       </c>
@@ -3022,46 +3013,38 @@
         <v>46006</v>
       </c>
     </row>
-    <row r="4" spans="1:12" s="6" customFormat="1" ht="13.8">
+    <row r="4" spans="1:10" s="6" customFormat="1" ht="13.8">
       <c r="E4" s="7"/>
       <c r="I4" s="74"/>
     </row>
-    <row r="5" spans="1:12" s="8" customFormat="1" ht="13.8">
+    <row r="5" spans="1:10" s="8" customFormat="1" ht="13.8">
       <c r="A5" s="8" t="s">
         <v>29</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F5" s="10"/>
     </row>
-    <row r="6" spans="1:12" s="8" customFormat="1" ht="13.8">
+    <row r="6" spans="1:10" s="8" customFormat="1" ht="13.8">
       <c r="B6" s="11"/>
       <c r="F6" s="12"/>
     </row>
-    <row r="7" spans="1:12" s="8" customFormat="1" ht="13.8">
+    <row r="7" spans="1:10" s="8" customFormat="1" ht="13.8">
       <c r="A7" s="8" t="s">
         <v>31</v>
       </c>
       <c r="B7" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="K7" s="178"/>
-    </row>
-    <row r="8" spans="1:12" s="8" customFormat="1" ht="13.8">
+    </row>
+    <row r="8" spans="1:10" s="8" customFormat="1" ht="13.8">
       <c r="B8" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="J8" s="178"/>
-      <c r="K8" s="178"/>
-      <c r="L8" s="178"/>
-    </row>
-    <row r="9" spans="1:12" s="8" customFormat="1" ht="13.8">
-      <c r="J9" s="178"/>
-      <c r="K9" s="178"/>
-      <c r="L9" s="178"/>
-    </row>
-    <row r="10" spans="1:12" s="8" customFormat="1" ht="13.8">
+    </row>
+    <row r="9" spans="1:10" s="8" customFormat="1" ht="13.8"/>
+    <row r="10" spans="1:10" s="8" customFormat="1" ht="13.8">
       <c r="A10" s="8" t="s">
         <v>34</v>
       </c>
@@ -3069,25 +3052,19 @@
         <v>97</v>
       </c>
       <c r="H10" s="6"/>
-      <c r="J10" s="178"/>
-      <c r="K10" s="178"/>
-      <c r="L10" s="178"/>
-    </row>
-    <row r="11" spans="1:12" s="8" customFormat="1" ht="13.8">
+    </row>
+    <row r="11" spans="1:10" s="8" customFormat="1" ht="13.8">
       <c r="B11" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="J11" s="178"/>
-      <c r="K11" s="178"/>
-      <c r="L11" s="178"/>
-    </row>
-    <row r="12" spans="1:12" s="8" customFormat="1" ht="13.8">
+    </row>
+    <row r="12" spans="1:10" s="8" customFormat="1" ht="13.8">
       <c r="B12" s="8" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:12" s="8" customFormat="1" ht="13.8"/>
-    <row r="14" spans="1:12" s="8" customFormat="1" ht="13.8">
+    <row r="13" spans="1:10" s="8" customFormat="1" ht="13.8"/>
+    <row r="14" spans="1:10" s="8" customFormat="1" ht="13.8">
       <c r="A14" s="8" t="s">
         <v>35</v>
       </c>
@@ -3101,8 +3078,8 @@
         <v>98</v>
       </c>
     </row>
-    <row r="15" spans="1:12" s="8" customFormat="1" ht="13.8"/>
-    <row r="16" spans="1:12" s="8" customFormat="1" ht="15">
+    <row r="15" spans="1:10" s="8" customFormat="1" ht="13.8"/>
+    <row r="16" spans="1:10" s="8" customFormat="1" ht="15">
       <c r="A16" s="12" t="s">
         <v>37</v>
       </c>
@@ -3110,23 +3087,20 @@
       <c r="C16" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="H16" s="179"/>
-      <c r="I16" s="184" t="s">
-        <v>173</v>
+      <c r="H16" s="146"/>
+      <c r="I16" s="151" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="17" spans="1:15" s="8" customFormat="1" ht="13.95" customHeight="1">
       <c r="A17" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="C17" s="8" t="s">
-        <v>171</v>
-      </c>
       <c r="E17" s="13"/>
-      <c r="H17" s="185" t="s">
+      <c r="H17" s="152" t="s">
         <v>39</v>
       </c>
-      <c r="I17" s="186">
+      <c r="I17" s="153">
         <v>8052.66</v>
       </c>
       <c r="M17" s="14"/>
@@ -3137,25 +3111,25 @@
       <c r="A18" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="C18" s="179" t="s">
+      <c r="C18" s="146" t="s">
+        <v>182</v>
+      </c>
+      <c r="D18" s="147" t="s">
+        <v>183</v>
+      </c>
+      <c r="E18" s="148" t="s">
+        <v>179</v>
+      </c>
+      <c r="F18" s="147" t="s">
         <v>184</v>
       </c>
-      <c r="D18" s="180" t="s">
-        <v>185</v>
-      </c>
-      <c r="E18" s="181" t="s">
-        <v>181</v>
-      </c>
-      <c r="F18" s="180" t="s">
-        <v>186</v>
-      </c>
-      <c r="G18" s="180" t="s">
-        <v>178</v>
-      </c>
-      <c r="H18" s="185" t="s">
+      <c r="G18" s="147" t="s">
+        <v>176</v>
+      </c>
+      <c r="H18" s="152" t="s">
         <v>40</v>
       </c>
-      <c r="I18" s="186">
+      <c r="I18" s="153">
         <v>65.040000000000006</v>
       </c>
       <c r="K18" s="15"/>
@@ -3167,23 +3141,23 @@
       <c r="A19" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="C19" s="179"/>
-      <c r="D19" s="182" t="s">
-        <v>179</v>
-      </c>
-      <c r="E19" s="181" t="s">
-        <v>180</v>
-      </c>
-      <c r="F19" s="183">
+      <c r="C19" s="146"/>
+      <c r="D19" s="149" t="s">
+        <v>177</v>
+      </c>
+      <c r="E19" s="148" t="s">
+        <v>178</v>
+      </c>
+      <c r="F19" s="150">
         <v>1534</v>
       </c>
-      <c r="G19" s="180">
+      <c r="G19" s="147">
         <v>1536</v>
       </c>
-      <c r="H19" s="185" t="s">
+      <c r="H19" s="152" t="s">
         <v>41</v>
       </c>
-      <c r="I19" s="187">
+      <c r="I19" s="154">
         <v>7119</v>
       </c>
       <c r="L19" s="18"/>
@@ -3194,10 +3168,10 @@
       </c>
       <c r="C20" s="9"/>
       <c r="F20" s="12"/>
-      <c r="H20" s="185" t="s">
+      <c r="H20" s="152" t="s">
         <v>38</v>
       </c>
-      <c r="I20" s="187">
+      <c r="I20" s="154">
         <v>894</v>
       </c>
     </row>
@@ -3207,18 +3181,18 @@
       </c>
       <c r="C21" s="20"/>
       <c r="E21" s="13"/>
-      <c r="H21" s="179"/>
-      <c r="I21" s="188" t="s">
-        <v>174</v>
+      <c r="H21" s="146"/>
+      <c r="I21" s="155" t="s">
+        <v>172</v>
       </c>
       <c r="J21" s="19"/>
     </row>
     <row r="22" spans="1:15" s="8" customFormat="1" ht="13.8">
       <c r="E22" s="13"/>
-      <c r="H22" s="185" t="s">
+      <c r="H22" s="152" t="s">
         <v>39</v>
       </c>
-      <c r="I22" s="186">
+      <c r="I22" s="153">
         <v>8052.66</v>
       </c>
     </row>
@@ -3227,31 +3201,31 @@
         <v>42</v>
       </c>
       <c r="E23" s="13"/>
-      <c r="H23" s="185" t="s">
+      <c r="H23" s="152" t="s">
         <v>40</v>
       </c>
-      <c r="I23" s="186">
+      <c r="I23" s="153">
         <v>65.040000000000006</v>
       </c>
     </row>
     <row r="24" spans="1:15" s="8" customFormat="1" ht="13.8">
       <c r="A24" s="19"/>
-      <c r="H24" s="185" t="s">
+      <c r="H24" s="152" t="s">
         <v>41</v>
       </c>
-      <c r="I24" s="187">
+      <c r="I24" s="154">
         <v>7119</v>
       </c>
       <c r="J24" s="19"/>
     </row>
     <row r="25" spans="1:15" s="8" customFormat="1" ht="13.8">
       <c r="C25" s="8" t="s">
-        <v>175</v>
-      </c>
-      <c r="H25" s="185" t="s">
+        <v>173</v>
+      </c>
+      <c r="H25" s="152" t="s">
         <v>38</v>
       </c>
-      <c r="I25" s="187">
+      <c r="I25" s="154">
         <v>894</v>
       </c>
       <c r="J25" s="19"/>
@@ -3259,19 +3233,19 @@
     <row r="26" spans="1:15" s="8" customFormat="1" ht="14.4">
       <c r="A26" s="19"/>
       <c r="C26" s="8" t="s">
-        <v>176</v>
-      </c>
-      <c r="H26" s="179"/>
-      <c r="I26" s="189" t="s">
-        <v>182</v>
+        <v>174</v>
+      </c>
+      <c r="H26" s="146"/>
+      <c r="I26" s="156" t="s">
+        <v>180</v>
       </c>
       <c r="J26" s="19"/>
     </row>
     <row r="27" spans="1:15" s="8" customFormat="1" ht="13.8">
-      <c r="H27" s="185" t="s">
+      <c r="H27" s="152" t="s">
         <v>39</v>
       </c>
-      <c r="I27" s="186">
+      <c r="I27" s="153">
         <v>8052.66</v>
       </c>
       <c r="J27" s="19"/>
@@ -3290,10 +3264,10 @@
       <c r="F28" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="H28" s="185" t="s">
+      <c r="H28" s="152" t="s">
         <v>40</v>
       </c>
-      <c r="I28" s="186">
+      <c r="I28" s="153">
         <v>65.040000000000006</v>
       </c>
       <c r="J28" s="19"/>
@@ -3306,19 +3280,19 @@
         <v>121</v>
       </c>
       <c r="C29" s="12"/>
-      <c r="H29" s="185" t="s">
+      <c r="H29" s="152" t="s">
         <v>41</v>
       </c>
-      <c r="I29" s="187">
+      <c r="I29" s="154">
         <v>7119</v>
       </c>
       <c r="J29" s="19"/>
     </row>
     <row r="30" spans="1:15" s="8" customFormat="1" ht="13.8">
-      <c r="H30" s="185" t="s">
+      <c r="H30" s="152" t="s">
         <v>38</v>
       </c>
-      <c r="I30" s="187">
+      <c r="I30" s="154">
         <v>894</v>
       </c>
       <c r="J30" s="19"/>
@@ -3360,10 +3334,10 @@
     </row>
     <row r="37" spans="1:10" s="24" customFormat="1">
       <c r="A37" s="25" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B37" s="144" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C37" s="81" t="s">
         <v>145</v>
@@ -3424,7 +3398,7 @@
     <row r="42" spans="1:10" s="24" customFormat="1">
       <c r="A42" s="32"/>
       <c r="B42" s="145" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C42" s="26"/>
       <c r="D42" s="26"/>
@@ -3582,15 +3556,15 @@
       <c r="D53" s="141" t="s">
         <v>166</v>
       </c>
-      <c r="E53" s="141" t="s">
-        <v>167</v>
+      <c r="E53" s="189" t="s">
+        <v>171</v>
       </c>
       <c r="F53" s="34"/>
       <c r="G53" s="34"/>
     </row>
     <row r="54" spans="1:1008" s="8" customFormat="1" ht="15">
       <c r="A54" s="34" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B54" s="34"/>
       <c r="C54" s="142" t="s">
@@ -3603,7 +3577,7 @@
     </row>
     <row r="55" spans="1:1008" s="8" customFormat="1" ht="15">
       <c r="A55" s="143" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B55" s="143"/>
       <c r="C55" s="142" t="s">
@@ -3616,7 +3590,7 @@
     </row>
     <row r="56" spans="1:1008" s="8" customFormat="1" ht="15">
       <c r="A56" s="143" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B56" s="143"/>
       <c r="C56" s="142" t="s">
@@ -3966,10 +3940,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="17.399999999999999">
-      <c r="A1" s="146" t="s">
+      <c r="A1" s="158" t="s">
         <v>61</v>
       </c>
-      <c r="B1" s="147"/>
+      <c r="B1" s="159"/>
       <c r="M1" s="38"/>
     </row>
     <row r="3" spans="1:13" ht="15" customHeight="1">
@@ -4311,27 +4285,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:49" ht="17.399999999999999">
-      <c r="A1" s="170" t="s">
+      <c r="A1" s="181" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="170"/>
-      <c r="C1" s="170"/>
-      <c r="D1" s="170"/>
-      <c r="E1" s="170"/>
-      <c r="F1" s="170"/>
-      <c r="G1" s="170"/>
-      <c r="H1" s="170"/>
-      <c r="I1" s="170"/>
-      <c r="J1" s="170"/>
-      <c r="K1" s="170"/>
-      <c r="L1" s="170"/>
-      <c r="M1" s="170"/>
-      <c r="N1" s="170"/>
-      <c r="O1" s="170"/>
-      <c r="P1" s="170"/>
-      <c r="Q1" s="170"/>
-      <c r="R1" s="170"/>
-      <c r="S1" s="170"/>
+      <c r="B1" s="181"/>
+      <c r="C1" s="181"/>
+      <c r="D1" s="181"/>
+      <c r="E1" s="181"/>
+      <c r="F1" s="181"/>
+      <c r="G1" s="181"/>
+      <c r="H1" s="181"/>
+      <c r="I1" s="181"/>
+      <c r="J1" s="181"/>
+      <c r="K1" s="181"/>
+      <c r="L1" s="181"/>
+      <c r="M1" s="181"/>
+      <c r="N1" s="181"/>
+      <c r="O1" s="181"/>
+      <c r="P1" s="181"/>
+      <c r="Q1" s="181"/>
+      <c r="R1" s="181"/>
+      <c r="S1" s="181"/>
     </row>
     <row r="2" spans="1:49" s="98" customFormat="1" ht="13.8">
       <c r="A2" s="95" t="s">
@@ -4349,10 +4323,10 @@
       <c r="L2" s="99"/>
       <c r="M2" s="101"/>
       <c r="N2" s="99"/>
-      <c r="O2" s="171" t="s">
+      <c r="O2" s="182" t="s">
         <v>158</v>
       </c>
-      <c r="P2" s="171"/>
+      <c r="P2" s="182"/>
       <c r="Q2" s="102" t="s">
         <v>3</v>
       </c>
@@ -4441,11 +4415,11 @@
       <c r="A6" s="95" t="s">
         <v>157</v>
       </c>
-      <c r="B6" s="172"/>
-      <c r="C6" s="172"/>
-      <c r="D6" s="172"/>
-      <c r="E6" s="172"/>
-      <c r="F6" s="172"/>
+      <c r="B6" s="183"/>
+      <c r="C6" s="183"/>
+      <c r="D6" s="183"/>
+      <c r="E6" s="183"/>
+      <c r="F6" s="183"/>
       <c r="G6" s="118"/>
       <c r="I6" s="99"/>
       <c r="J6" s="100"/>
@@ -4479,70 +4453,70 @@
       <c r="S7" s="88"/>
     </row>
     <row r="8" spans="1:49" s="90" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A8" s="173" t="s">
+      <c r="A8" s="184" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="174" t="s">
+      <c r="B8" s="185" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="174" t="s">
+      <c r="C8" s="185" t="s">
         <v>11</v>
       </c>
-      <c r="D8" s="174"/>
-      <c r="E8" s="174"/>
-      <c r="F8" s="174" t="s">
+      <c r="D8" s="185"/>
+      <c r="E8" s="185"/>
+      <c r="F8" s="185" t="s">
         <v>12</v>
       </c>
-      <c r="G8" s="175" t="s">
+      <c r="G8" s="186" t="s">
         <v>13</v>
       </c>
-      <c r="H8" s="175" t="s">
+      <c r="H8" s="186" t="s">
         <v>14</v>
       </c>
-      <c r="I8" s="175" t="s">
+      <c r="I8" s="186" t="s">
         <v>15</v>
       </c>
-      <c r="J8" s="176" t="s">
+      <c r="J8" s="187" t="s">
         <v>16</v>
       </c>
-      <c r="K8" s="173" t="s">
+      <c r="K8" s="184" t="s">
         <v>17</v>
       </c>
-      <c r="L8" s="174" t="s">
+      <c r="L8" s="185" t="s">
         <v>153</v>
       </c>
-      <c r="M8" s="174"/>
-      <c r="N8" s="174"/>
-      <c r="O8" s="174"/>
-      <c r="P8" s="177" t="s">
+      <c r="M8" s="185"/>
+      <c r="N8" s="185"/>
+      <c r="O8" s="185"/>
+      <c r="P8" s="188" t="s">
         <v>18</v>
       </c>
-      <c r="Q8" s="177"/>
-      <c r="R8" s="177"/>
+      <c r="Q8" s="188"/>
+      <c r="R8" s="188"/>
       <c r="S8" s="89" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:49" s="90" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A9" s="173"/>
-      <c r="B9" s="174"/>
-      <c r="C9" s="174"/>
-      <c r="D9" s="174"/>
-      <c r="E9" s="174"/>
-      <c r="F9" s="174"/>
-      <c r="G9" s="175"/>
-      <c r="H9" s="175"/>
-      <c r="I9" s="175"/>
-      <c r="J9" s="176"/>
-      <c r="K9" s="176"/>
-      <c r="L9" s="174" t="s">
+      <c r="A9" s="184"/>
+      <c r="B9" s="185"/>
+      <c r="C9" s="185"/>
+      <c r="D9" s="185"/>
+      <c r="E9" s="185"/>
+      <c r="F9" s="185"/>
+      <c r="G9" s="186"/>
+      <c r="H9" s="186"/>
+      <c r="I9" s="186"/>
+      <c r="J9" s="187"/>
+      <c r="K9" s="187"/>
+      <c r="L9" s="185" t="s">
         <v>20</v>
       </c>
-      <c r="M9" s="174"/>
-      <c r="N9" s="174" t="s">
+      <c r="M9" s="185"/>
+      <c r="N9" s="185" t="s">
         <v>21</v>
       </c>
-      <c r="O9" s="174"/>
+      <c r="O9" s="185"/>
       <c r="P9" s="91" t="s">
         <v>22</v>
       </c>
@@ -4557,10 +4531,10 @@
       </c>
     </row>
     <row r="10" spans="1:49" s="115" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A10" s="155" t="s">
+      <c r="A10" s="166" t="s">
         <v>150</v>
       </c>
-      <c r="B10" s="157" t="s">
+      <c r="B10" s="168" t="s">
         <v>151</v>
       </c>
       <c r="C10" s="109">
@@ -4588,7 +4562,7 @@
         <f>SUM(H10*I10)</f>
         <v>180</v>
       </c>
-      <c r="K10" s="159">
+      <c r="K10" s="170">
         <f>SUM(J10:J12)</f>
         <v>660</v>
       </c>
@@ -4621,8 +4595,8 @@
       </c>
     </row>
     <row r="11" spans="1:49" s="115" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A11" s="156"/>
-      <c r="B11" s="158"/>
+      <c r="A11" s="167"/>
+      <c r="B11" s="169"/>
       <c r="C11" s="109">
         <v>31</v>
       </c>
@@ -4648,7 +4622,7 @@
         <f>SUM(H11*I11)</f>
         <v>240</v>
       </c>
-      <c r="K11" s="160"/>
+      <c r="K11" s="171"/>
       <c r="L11" s="113">
         <v>4.5999999999999996</v>
       </c>
@@ -4678,8 +4652,8 @@
       </c>
     </row>
     <row r="12" spans="1:49" s="115" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A12" s="156"/>
-      <c r="B12" s="158"/>
+      <c r="A12" s="167"/>
+      <c r="B12" s="169"/>
       <c r="C12" s="109">
         <v>71</v>
       </c>
@@ -4705,7 +4679,7 @@
         <f>SUM(H12*I12)</f>
         <v>240</v>
       </c>
-      <c r="K12" s="160"/>
+      <c r="K12" s="171"/>
       <c r="L12" s="113">
         <v>4.5999999999999996</v>
       </c>
@@ -4735,10 +4709,10 @@
       </c>
     </row>
     <row r="13" spans="1:49" s="125" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A13" s="161" t="s">
+      <c r="A13" s="172" t="s">
         <v>111</v>
       </c>
-      <c r="B13" s="164" t="s">
+      <c r="B13" s="175" t="s">
         <v>127</v>
       </c>
       <c r="C13" s="120">
@@ -4766,7 +4740,7 @@
         <f t="shared" ref="J13:J76" si="0">H13*I13</f>
         <v>420</v>
       </c>
-      <c r="K13" s="167">
+      <c r="K13" s="178">
         <f>SUM(J13:J16)</f>
         <v>1500</v>
       </c>
@@ -4829,8 +4803,8 @@
       <c r="AW13" s="136"/>
     </row>
     <row r="14" spans="1:49" s="125" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A14" s="162"/>
-      <c r="B14" s="165"/>
+      <c r="A14" s="173"/>
+      <c r="B14" s="176"/>
       <c r="C14" s="120">
         <f t="shared" ref="C14:C18" si="4">E13+1</f>
         <v>269</v>
@@ -4858,7 +4832,7 @@
         <f t="shared" si="0"/>
         <v>600</v>
       </c>
-      <c r="K14" s="168"/>
+      <c r="K14" s="179"/>
       <c r="L14" s="124">
         <v>9</v>
       </c>
@@ -4918,8 +4892,8 @@
       <c r="AW14" s="136"/>
     </row>
     <row r="15" spans="1:49" s="125" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A15" s="162"/>
-      <c r="B15" s="165"/>
+      <c r="A15" s="173"/>
+      <c r="B15" s="176"/>
       <c r="C15" s="120">
         <v>424</v>
       </c>
@@ -4945,7 +4919,7 @@
         <f t="shared" si="0"/>
         <v>180</v>
       </c>
-      <c r="K15" s="168"/>
+      <c r="K15" s="179"/>
       <c r="L15" s="124">
         <v>9</v>
       </c>
@@ -5005,8 +4979,8 @@
       <c r="AW15" s="136"/>
     </row>
     <row r="16" spans="1:49" s="125" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A16" s="163"/>
-      <c r="B16" s="166"/>
+      <c r="A16" s="174"/>
+      <c r="B16" s="177"/>
       <c r="C16" s="120">
         <f t="shared" si="4"/>
         <v>439</v>
@@ -5034,7 +5008,7 @@
         <f t="shared" si="0"/>
         <v>300</v>
       </c>
-      <c r="K16" s="169"/>
+      <c r="K16" s="180"/>
       <c r="L16" s="124">
         <v>9</v>
       </c>
@@ -5094,10 +5068,10 @@
       <c r="AW16" s="136"/>
     </row>
     <row r="17" spans="1:49" s="125" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A17" s="161" t="s">
+      <c r="A17" s="172" t="s">
         <v>112</v>
       </c>
-      <c r="B17" s="164" t="s">
+      <c r="B17" s="175" t="s">
         <v>130</v>
       </c>
       <c r="C17" s="120">
@@ -5125,7 +5099,7 @@
         <f t="shared" si="0"/>
         <v>240</v>
       </c>
-      <c r="K17" s="167">
+      <c r="K17" s="178">
         <f>SUM(J17:J21)</f>
         <v>1416</v>
       </c>
@@ -5188,8 +5162,8 @@
       <c r="AW17" s="136"/>
     </row>
     <row r="18" spans="1:49" s="125" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A18" s="162"/>
-      <c r="B18" s="165"/>
+      <c r="A18" s="173"/>
+      <c r="B18" s="176"/>
       <c r="C18" s="120">
         <f t="shared" si="4"/>
         <v>106</v>
@@ -5217,7 +5191,7 @@
         <f t="shared" si="0"/>
         <v>360</v>
       </c>
-      <c r="K18" s="168"/>
+      <c r="K18" s="179"/>
       <c r="L18" s="124">
         <v>9</v>
       </c>
@@ -5277,8 +5251,8 @@
       <c r="AW18" s="136"/>
     </row>
     <row r="19" spans="1:49" s="125" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A19" s="162"/>
-      <c r="B19" s="165"/>
+      <c r="A19" s="173"/>
+      <c r="B19" s="176"/>
       <c r="C19" s="120">
         <v>136</v>
       </c>
@@ -5304,7 +5278,7 @@
         <f t="shared" si="0"/>
         <v>96</v>
       </c>
-      <c r="K19" s="168"/>
+      <c r="K19" s="179"/>
       <c r="L19" s="124">
         <v>9</v>
       </c>
@@ -5364,8 +5338,8 @@
       <c r="AW19" s="136"/>
     </row>
     <row r="20" spans="1:49" s="125" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A20" s="162"/>
-      <c r="B20" s="165"/>
+      <c r="A20" s="173"/>
+      <c r="B20" s="176"/>
       <c r="C20" s="120">
         <f t="shared" ref="C20:C24" si="6">E19+1</f>
         <v>144</v>
@@ -5393,7 +5367,7 @@
         <f t="shared" si="0"/>
         <v>300</v>
       </c>
-      <c r="K20" s="168"/>
+      <c r="K20" s="179"/>
       <c r="L20" s="124">
         <v>9</v>
       </c>
@@ -5453,8 +5427,8 @@
       <c r="AW20" s="136"/>
     </row>
     <row r="21" spans="1:49" s="125" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A21" s="163"/>
-      <c r="B21" s="166"/>
+      <c r="A21" s="174"/>
+      <c r="B21" s="177"/>
       <c r="C21" s="120">
         <f t="shared" si="6"/>
         <v>169</v>
@@ -5482,7 +5456,7 @@
         <f t="shared" si="0"/>
         <v>420</v>
       </c>
-      <c r="K21" s="169"/>
+      <c r="K21" s="180"/>
       <c r="L21" s="124">
         <v>9</v>
       </c>
@@ -5542,10 +5516,10 @@
       <c r="AW21" s="136"/>
     </row>
     <row r="22" spans="1:49" s="125" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A22" s="149" t="s">
+      <c r="A22" s="160" t="s">
         <v>122</v>
       </c>
-      <c r="B22" s="150" t="s">
+      <c r="B22" s="161" t="s">
         <v>133</v>
       </c>
       <c r="C22" s="120">
@@ -5573,7 +5547,7 @@
         <f t="shared" si="0"/>
         <v>120</v>
       </c>
-      <c r="K22" s="151">
+      <c r="K22" s="162">
         <f>SUM(J22:J24)</f>
         <v>210</v>
       </c>
@@ -5636,8 +5610,8 @@
       <c r="AW22" s="136"/>
     </row>
     <row r="23" spans="1:49" s="125" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A23" s="149"/>
-      <c r="B23" s="150"/>
+      <c r="A23" s="160"/>
+      <c r="B23" s="161"/>
       <c r="C23" s="120">
         <f t="shared" si="6"/>
         <v>21</v>
@@ -5665,7 +5639,7 @@
         <f t="shared" si="0"/>
         <v>60</v>
       </c>
-      <c r="K23" s="151"/>
+      <c r="K23" s="162"/>
       <c r="L23" s="124">
         <v>4.3</v>
       </c>
@@ -5725,8 +5699,8 @@
       <c r="AW23" s="136"/>
     </row>
     <row r="24" spans="1:49" s="125" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A24" s="149"/>
-      <c r="B24" s="150"/>
+      <c r="A24" s="160"/>
+      <c r="B24" s="161"/>
       <c r="C24" s="120">
         <f t="shared" si="6"/>
         <v>31</v>
@@ -5754,7 +5728,7 @@
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="K24" s="151"/>
+      <c r="K24" s="162"/>
       <c r="L24" s="124">
         <v>4.3</v>
       </c>
@@ -5814,10 +5788,10 @@
       <c r="AW24" s="136"/>
     </row>
     <row r="25" spans="1:49" s="125" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A25" s="149" t="s">
+      <c r="A25" s="160" t="s">
         <v>123</v>
       </c>
-      <c r="B25" s="150" t="s">
+      <c r="B25" s="161" t="s">
         <v>124</v>
       </c>
       <c r="C25" s="120">
@@ -5845,7 +5819,7 @@
         <f t="shared" si="0"/>
         <v>210</v>
       </c>
-      <c r="K25" s="151">
+      <c r="K25" s="162">
         <f>SUM(J25:J27)</f>
         <v>330</v>
       </c>
@@ -5908,8 +5882,8 @@
       <c r="AW25" s="136"/>
     </row>
     <row r="26" spans="1:49" s="125" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A26" s="149"/>
-      <c r="B26" s="150"/>
+      <c r="A26" s="160"/>
+      <c r="B26" s="161"/>
       <c r="C26" s="120">
         <f t="shared" ref="C26:C30" si="8">E25+1</f>
         <v>36</v>
@@ -5937,7 +5911,7 @@
         <f t="shared" si="0"/>
         <v>60</v>
       </c>
-      <c r="K26" s="151"/>
+      <c r="K26" s="162"/>
       <c r="L26" s="124">
         <v>5</v>
       </c>
@@ -5997,8 +5971,8 @@
       <c r="AW26" s="136"/>
     </row>
     <row r="27" spans="1:49" s="125" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A27" s="149"/>
-      <c r="B27" s="150"/>
+      <c r="A27" s="160"/>
+      <c r="B27" s="161"/>
       <c r="C27" s="120">
         <f t="shared" si="8"/>
         <v>46</v>
@@ -6026,7 +6000,7 @@
         <f t="shared" si="0"/>
         <v>60</v>
       </c>
-      <c r="K27" s="151"/>
+      <c r="K27" s="162"/>
       <c r="L27" s="124">
         <v>5</v>
       </c>
@@ -6086,10 +6060,10 @@
       <c r="AW27" s="136"/>
     </row>
     <row r="28" spans="1:49" s="125" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A28" s="149" t="s">
+      <c r="A28" s="160" t="s">
         <v>125</v>
       </c>
-      <c r="B28" s="150" t="s">
+      <c r="B28" s="161" t="s">
         <v>124</v>
       </c>
       <c r="C28" s="120">
@@ -6117,7 +6091,7 @@
         <f t="shared" si="0"/>
         <v>300</v>
       </c>
-      <c r="K28" s="151">
+      <c r="K28" s="162">
         <f>SUM(J28:J30)</f>
         <v>420</v>
       </c>
@@ -6180,8 +6154,8 @@
       <c r="AW28" s="136"/>
     </row>
     <row r="29" spans="1:49" s="125" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A29" s="149"/>
-      <c r="B29" s="150"/>
+      <c r="A29" s="160"/>
+      <c r="B29" s="161"/>
       <c r="C29" s="120">
         <f t="shared" si="8"/>
         <v>51</v>
@@ -6209,7 +6183,7 @@
         <f t="shared" si="0"/>
         <v>60</v>
       </c>
-      <c r="K29" s="151"/>
+      <c r="K29" s="162"/>
       <c r="L29" s="124">
         <v>5</v>
       </c>
@@ -6269,8 +6243,8 @@
       <c r="AW29" s="136"/>
     </row>
     <row r="30" spans="1:49" s="125" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A30" s="149"/>
-      <c r="B30" s="150"/>
+      <c r="A30" s="160"/>
+      <c r="B30" s="161"/>
       <c r="C30" s="120">
         <f t="shared" si="8"/>
         <v>61</v>
@@ -6298,7 +6272,7 @@
         <f t="shared" si="0"/>
         <v>60</v>
       </c>
-      <c r="K30" s="151"/>
+      <c r="K30" s="162"/>
       <c r="L30" s="124">
         <v>5</v>
       </c>
@@ -6358,10 +6332,10 @@
       <c r="AW30" s="136"/>
     </row>
     <row r="31" spans="1:49" s="125" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A31" s="149" t="s">
+      <c r="A31" s="160" t="s">
         <v>138</v>
       </c>
-      <c r="B31" s="150" t="s">
+      <c r="B31" s="161" t="s">
         <v>126</v>
       </c>
       <c r="C31" s="120">
@@ -6389,7 +6363,7 @@
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="K31" s="151">
+      <c r="K31" s="162">
         <f>SUM(J31:J67)</f>
         <v>687</v>
       </c>
@@ -6452,8 +6426,8 @@
       <c r="AW31" s="136"/>
     </row>
     <row r="32" spans="1:49" s="125" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A32" s="149"/>
-      <c r="B32" s="150"/>
+      <c r="A32" s="160"/>
+      <c r="B32" s="161"/>
       <c r="C32" s="120">
         <f t="shared" ref="C32:C67" si="10">E31+1</f>
         <v>2</v>
@@ -6481,7 +6455,7 @@
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="K32" s="151"/>
+      <c r="K32" s="162"/>
       <c r="L32" s="124">
         <v>6</v>
       </c>
@@ -6541,8 +6515,8 @@
       <c r="AW32" s="136"/>
     </row>
     <row r="33" spans="1:49" s="125" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A33" s="149"/>
-      <c r="B33" s="150"/>
+      <c r="A33" s="160"/>
+      <c r="B33" s="161"/>
       <c r="C33" s="120">
         <f t="shared" si="10"/>
         <v>3</v>
@@ -6570,7 +6544,7 @@
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="K33" s="151"/>
+      <c r="K33" s="162"/>
       <c r="L33" s="124">
         <v>6</v>
       </c>
@@ -6630,8 +6604,8 @@
       <c r="AW33" s="136"/>
     </row>
     <row r="34" spans="1:49" s="125" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A34" s="149"/>
-      <c r="B34" s="150"/>
+      <c r="A34" s="160"/>
+      <c r="B34" s="161"/>
       <c r="C34" s="120">
         <f t="shared" si="10"/>
         <v>4</v>
@@ -6659,7 +6633,7 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="K34" s="151"/>
+      <c r="K34" s="162"/>
       <c r="L34" s="124">
         <v>4</v>
       </c>
@@ -6719,8 +6693,8 @@
       <c r="AW34" s="136"/>
     </row>
     <row r="35" spans="1:49" s="125" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A35" s="149"/>
-      <c r="B35" s="150"/>
+      <c r="A35" s="160"/>
+      <c r="B35" s="161"/>
       <c r="C35" s="120">
         <f t="shared" si="10"/>
         <v>5</v>
@@ -6748,7 +6722,7 @@
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="K35" s="151"/>
+      <c r="K35" s="162"/>
       <c r="L35" s="124">
         <v>6</v>
       </c>
@@ -6808,8 +6782,8 @@
       <c r="AW35" s="136"/>
     </row>
     <row r="36" spans="1:49" s="125" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A36" s="149"/>
-      <c r="B36" s="150"/>
+      <c r="A36" s="160"/>
+      <c r="B36" s="161"/>
       <c r="C36" s="120">
         <f t="shared" si="10"/>
         <v>7</v>
@@ -6837,7 +6811,7 @@
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="K36" s="151"/>
+      <c r="K36" s="162"/>
       <c r="L36" s="124">
         <v>8</v>
       </c>
@@ -6897,8 +6871,8 @@
       <c r="AW36" s="136"/>
     </row>
     <row r="37" spans="1:49" s="125" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A37" s="149"/>
-      <c r="B37" s="150"/>
+      <c r="A37" s="160"/>
+      <c r="B37" s="161"/>
       <c r="C37" s="120">
         <f t="shared" si="10"/>
         <v>9</v>
@@ -6926,7 +6900,7 @@
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="K37" s="151"/>
+      <c r="K37" s="162"/>
       <c r="L37" s="124">
         <v>6</v>
       </c>
@@ -6986,8 +6960,8 @@
       <c r="AW37" s="136"/>
     </row>
     <row r="38" spans="1:49" s="125" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A38" s="149"/>
-      <c r="B38" s="150"/>
+      <c r="A38" s="160"/>
+      <c r="B38" s="161"/>
       <c r="C38" s="120">
         <f t="shared" si="10"/>
         <v>11</v>
@@ -7015,7 +6989,7 @@
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="K38" s="151"/>
+      <c r="K38" s="162"/>
       <c r="L38" s="124">
         <v>8</v>
       </c>
@@ -7075,8 +7049,8 @@
       <c r="AW38" s="136"/>
     </row>
     <row r="39" spans="1:49" s="125" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A39" s="149"/>
-      <c r="B39" s="150"/>
+      <c r="A39" s="160"/>
+      <c r="B39" s="161"/>
       <c r="C39" s="120">
         <f t="shared" si="10"/>
         <v>14</v>
@@ -7104,7 +7078,7 @@
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="K39" s="151"/>
+      <c r="K39" s="162"/>
       <c r="L39" s="124">
         <v>8</v>
       </c>
@@ -7164,8 +7138,8 @@
       <c r="AW39" s="136"/>
     </row>
     <row r="40" spans="1:49" s="125" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A40" s="149"/>
-      <c r="B40" s="150"/>
+      <c r="A40" s="160"/>
+      <c r="B40" s="161"/>
       <c r="C40" s="120">
         <f t="shared" si="10"/>
         <v>16</v>
@@ -7193,7 +7167,7 @@
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="K40" s="151"/>
+      <c r="K40" s="162"/>
       <c r="L40" s="124">
         <v>8</v>
       </c>
@@ -7253,8 +7227,8 @@
       <c r="AW40" s="136"/>
     </row>
     <row r="41" spans="1:49" s="125" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A41" s="149"/>
-      <c r="B41" s="150"/>
+      <c r="A41" s="160"/>
+      <c r="B41" s="161"/>
       <c r="C41" s="120">
         <f t="shared" si="10"/>
         <v>19</v>
@@ -7282,7 +7256,7 @@
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="K41" s="151"/>
+      <c r="K41" s="162"/>
       <c r="L41" s="124">
         <v>8</v>
       </c>
@@ -7342,8 +7316,8 @@
       <c r="AW41" s="136"/>
     </row>
     <row r="42" spans="1:49" s="125" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A42" s="149"/>
-      <c r="B42" s="150"/>
+      <c r="A42" s="160"/>
+      <c r="B42" s="161"/>
       <c r="C42" s="120">
         <f t="shared" si="10"/>
         <v>22</v>
@@ -7371,7 +7345,7 @@
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="K42" s="151"/>
+      <c r="K42" s="162"/>
       <c r="L42" s="124">
         <v>8</v>
       </c>
@@ -7431,8 +7405,8 @@
       <c r="AW42" s="136"/>
     </row>
     <row r="43" spans="1:49" s="125" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A43" s="149"/>
-      <c r="B43" s="150"/>
+      <c r="A43" s="160"/>
+      <c r="B43" s="161"/>
       <c r="C43" s="120">
         <f t="shared" si="10"/>
         <v>24</v>
@@ -7460,7 +7434,7 @@
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="K43" s="151"/>
+      <c r="K43" s="162"/>
       <c r="L43" s="124">
         <v>8</v>
       </c>
@@ -7520,8 +7494,8 @@
       <c r="AW43" s="136"/>
     </row>
     <row r="44" spans="1:49" s="125" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A44" s="149"/>
-      <c r="B44" s="150"/>
+      <c r="A44" s="160"/>
+      <c r="B44" s="161"/>
       <c r="C44" s="120">
         <f t="shared" si="10"/>
         <v>25</v>
@@ -7549,7 +7523,7 @@
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="K44" s="151"/>
+      <c r="K44" s="162"/>
       <c r="L44" s="124">
         <v>6</v>
       </c>
@@ -7609,8 +7583,8 @@
       <c r="AW44" s="136"/>
     </row>
     <row r="45" spans="1:49" s="125" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A45" s="149"/>
-      <c r="B45" s="150"/>
+      <c r="A45" s="160"/>
+      <c r="B45" s="161"/>
       <c r="C45" s="120">
         <f t="shared" si="10"/>
         <v>26</v>
@@ -7638,7 +7612,7 @@
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="K45" s="151"/>
+      <c r="K45" s="162"/>
       <c r="L45" s="124">
         <v>6</v>
       </c>
@@ -7698,8 +7672,8 @@
       <c r="AW45" s="136"/>
     </row>
     <row r="46" spans="1:49" s="125" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A46" s="149"/>
-      <c r="B46" s="150"/>
+      <c r="A46" s="160"/>
+      <c r="B46" s="161"/>
       <c r="C46" s="120">
         <f t="shared" si="10"/>
         <v>27</v>
@@ -7727,7 +7701,7 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="K46" s="151"/>
+      <c r="K46" s="162"/>
       <c r="L46" s="124">
         <v>4</v>
       </c>
@@ -7787,8 +7761,8 @@
       <c r="AW46" s="136"/>
     </row>
     <row r="47" spans="1:49" s="125" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A47" s="149"/>
-      <c r="B47" s="150"/>
+      <c r="A47" s="160"/>
+      <c r="B47" s="161"/>
       <c r="C47" s="120">
         <f t="shared" si="10"/>
         <v>28</v>
@@ -7816,7 +7790,7 @@
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="K47" s="151"/>
+      <c r="K47" s="162"/>
       <c r="L47" s="124">
         <v>6</v>
       </c>
@@ -7876,8 +7850,8 @@
       <c r="AW47" s="136"/>
     </row>
     <row r="48" spans="1:49" s="125" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A48" s="149"/>
-      <c r="B48" s="150"/>
+      <c r="A48" s="160"/>
+      <c r="B48" s="161"/>
       <c r="C48" s="120">
         <f t="shared" si="10"/>
         <v>30</v>
@@ -7905,7 +7879,7 @@
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="K48" s="151"/>
+      <c r="K48" s="162"/>
       <c r="L48" s="124">
         <v>8</v>
       </c>
@@ -7965,8 +7939,8 @@
       <c r="AW48" s="136"/>
     </row>
     <row r="49" spans="1:49" s="125" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A49" s="149"/>
-      <c r="B49" s="150"/>
+      <c r="A49" s="160"/>
+      <c r="B49" s="161"/>
       <c r="C49" s="120">
         <f t="shared" si="10"/>
         <v>32</v>
@@ -7994,7 +7968,7 @@
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="K49" s="151"/>
+      <c r="K49" s="162"/>
       <c r="L49" s="124">
         <v>6</v>
       </c>
@@ -8054,8 +8028,8 @@
       <c r="AW49" s="136"/>
     </row>
     <row r="50" spans="1:49" s="125" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A50" s="149"/>
-      <c r="B50" s="150"/>
+      <c r="A50" s="160"/>
+      <c r="B50" s="161"/>
       <c r="C50" s="120">
         <f t="shared" si="10"/>
         <v>34</v>
@@ -8083,7 +8057,7 @@
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="K50" s="151"/>
+      <c r="K50" s="162"/>
       <c r="L50" s="124">
         <v>8</v>
       </c>
@@ -8143,8 +8117,8 @@
       <c r="AW50" s="136"/>
     </row>
     <row r="51" spans="1:49" s="125" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A51" s="149"/>
-      <c r="B51" s="150"/>
+      <c r="A51" s="160"/>
+      <c r="B51" s="161"/>
       <c r="C51" s="120">
         <f t="shared" si="10"/>
         <v>37</v>
@@ -8172,7 +8146,7 @@
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="K51" s="151"/>
+      <c r="K51" s="162"/>
       <c r="L51" s="124">
         <v>8</v>
       </c>
@@ -8232,8 +8206,8 @@
       <c r="AW51" s="136"/>
     </row>
     <row r="52" spans="1:49" s="125" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A52" s="149"/>
-      <c r="B52" s="150"/>
+      <c r="A52" s="160"/>
+      <c r="B52" s="161"/>
       <c r="C52" s="120">
         <f t="shared" si="10"/>
         <v>39</v>
@@ -8261,7 +8235,7 @@
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="K52" s="151"/>
+      <c r="K52" s="162"/>
       <c r="L52" s="124">
         <v>8</v>
       </c>
@@ -8321,8 +8295,8 @@
       <c r="AW52" s="136"/>
     </row>
     <row r="53" spans="1:49" s="125" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A53" s="149"/>
-      <c r="B53" s="150"/>
+      <c r="A53" s="160"/>
+      <c r="B53" s="161"/>
       <c r="C53" s="120">
         <f t="shared" si="10"/>
         <v>42</v>
@@ -8350,7 +8324,7 @@
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="K53" s="151"/>
+      <c r="K53" s="162"/>
       <c r="L53" s="124">
         <v>8</v>
       </c>
@@ -8410,8 +8384,8 @@
       <c r="AW53" s="136"/>
     </row>
     <row r="54" spans="1:49" s="125" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A54" s="149"/>
-      <c r="B54" s="150"/>
+      <c r="A54" s="160"/>
+      <c r="B54" s="161"/>
       <c r="C54" s="120">
         <f t="shared" si="10"/>
         <v>45</v>
@@ -8439,7 +8413,7 @@
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="K54" s="151"/>
+      <c r="K54" s="162"/>
       <c r="L54" s="124">
         <v>8</v>
       </c>
@@ -8499,8 +8473,8 @@
       <c r="AW54" s="136"/>
     </row>
     <row r="55" spans="1:49" s="125" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A55" s="149"/>
-      <c r="B55" s="150"/>
+      <c r="A55" s="160"/>
+      <c r="B55" s="161"/>
       <c r="C55" s="120">
         <f t="shared" si="10"/>
         <v>47</v>
@@ -8528,7 +8502,7 @@
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="K55" s="151"/>
+      <c r="K55" s="162"/>
       <c r="L55" s="124">
         <v>6</v>
       </c>
@@ -8588,8 +8562,8 @@
       <c r="AW55" s="136"/>
     </row>
     <row r="56" spans="1:49" s="125" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A56" s="149"/>
-      <c r="B56" s="150"/>
+      <c r="A56" s="160"/>
+      <c r="B56" s="161"/>
       <c r="C56" s="120">
         <f t="shared" si="10"/>
         <v>48</v>
@@ -8617,7 +8591,7 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="K56" s="151"/>
+      <c r="K56" s="162"/>
       <c r="L56" s="124">
         <v>4</v>
       </c>
@@ -8677,8 +8651,8 @@
       <c r="AW56" s="136"/>
     </row>
     <row r="57" spans="1:49" s="125" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A57" s="149"/>
-      <c r="B57" s="150"/>
+      <c r="A57" s="160"/>
+      <c r="B57" s="161"/>
       <c r="C57" s="120">
         <f t="shared" si="10"/>
         <v>49</v>
@@ -8706,7 +8680,7 @@
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="K57" s="151"/>
+      <c r="K57" s="162"/>
       <c r="L57" s="124">
         <v>8</v>
       </c>
@@ -8766,8 +8740,8 @@
       <c r="AW57" s="136"/>
     </row>
     <row r="58" spans="1:49" s="125" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A58" s="149"/>
-      <c r="B58" s="150"/>
+      <c r="A58" s="160"/>
+      <c r="B58" s="161"/>
       <c r="C58" s="120">
         <f t="shared" si="10"/>
         <v>50</v>
@@ -8795,7 +8769,7 @@
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="K58" s="151"/>
+      <c r="K58" s="162"/>
       <c r="L58" s="124">
         <v>6</v>
       </c>
@@ -8855,8 +8829,8 @@
       <c r="AW58" s="136"/>
     </row>
     <row r="59" spans="1:49" s="125" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A59" s="149"/>
-      <c r="B59" s="150"/>
+      <c r="A59" s="160"/>
+      <c r="B59" s="161"/>
       <c r="C59" s="120">
         <f t="shared" si="10"/>
         <v>51</v>
@@ -8884,7 +8858,7 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="K59" s="151"/>
+      <c r="K59" s="162"/>
       <c r="L59" s="124">
         <v>4</v>
       </c>
@@ -8944,8 +8918,8 @@
       <c r="AW59" s="136"/>
     </row>
     <row r="60" spans="1:49" s="125" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A60" s="149"/>
-      <c r="B60" s="150"/>
+      <c r="A60" s="160"/>
+      <c r="B60" s="161"/>
       <c r="C60" s="120">
         <f t="shared" si="10"/>
         <v>52</v>
@@ -8973,7 +8947,7 @@
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="K60" s="151"/>
+      <c r="K60" s="162"/>
       <c r="L60" s="124">
         <v>6</v>
       </c>
@@ -9033,8 +9007,8 @@
       <c r="AW60" s="136"/>
     </row>
     <row r="61" spans="1:49" s="125" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A61" s="149"/>
-      <c r="B61" s="150"/>
+      <c r="A61" s="160"/>
+      <c r="B61" s="161"/>
       <c r="C61" s="120">
         <f t="shared" si="10"/>
         <v>54</v>
@@ -9062,7 +9036,7 @@
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="K61" s="151"/>
+      <c r="K61" s="162"/>
       <c r="L61" s="124">
         <v>6</v>
       </c>
@@ -9122,8 +9096,8 @@
       <c r="AW61" s="136"/>
     </row>
     <row r="62" spans="1:49" s="125" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A62" s="149"/>
-      <c r="B62" s="150"/>
+      <c r="A62" s="160"/>
+      <c r="B62" s="161"/>
       <c r="C62" s="120">
         <f t="shared" si="10"/>
         <v>55</v>
@@ -9151,7 +9125,7 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="K62" s="151"/>
+      <c r="K62" s="162"/>
       <c r="L62" s="124">
         <v>4</v>
       </c>
@@ -9211,8 +9185,8 @@
       <c r="AW62" s="136"/>
     </row>
     <row r="63" spans="1:49" s="125" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A63" s="149"/>
-      <c r="B63" s="150"/>
+      <c r="A63" s="160"/>
+      <c r="B63" s="161"/>
       <c r="C63" s="120">
         <f t="shared" si="10"/>
         <v>56</v>
@@ -9240,7 +9214,7 @@
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="K63" s="151"/>
+      <c r="K63" s="162"/>
       <c r="L63" s="124">
         <v>8</v>
       </c>
@@ -9300,8 +9274,8 @@
       <c r="AW63" s="136"/>
     </row>
     <row r="64" spans="1:49" s="125" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A64" s="149"/>
-      <c r="B64" s="150"/>
+      <c r="A64" s="160"/>
+      <c r="B64" s="161"/>
       <c r="C64" s="120">
         <f t="shared" si="10"/>
         <v>58</v>
@@ -9329,7 +9303,7 @@
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="K64" s="151"/>
+      <c r="K64" s="162"/>
       <c r="L64" s="124">
         <v>6</v>
       </c>
@@ -9389,8 +9363,8 @@
       <c r="AW64" s="136"/>
     </row>
     <row r="65" spans="1:49" s="125" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A65" s="149"/>
-      <c r="B65" s="150"/>
+      <c r="A65" s="160"/>
+      <c r="B65" s="161"/>
       <c r="C65" s="120">
         <f t="shared" si="10"/>
         <v>60</v>
@@ -9418,7 +9392,7 @@
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="K65" s="151"/>
+      <c r="K65" s="162"/>
       <c r="L65" s="124">
         <v>8</v>
       </c>
@@ -9478,8 +9452,8 @@
       <c r="AW65" s="136"/>
     </row>
     <row r="66" spans="1:49" s="125" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A66" s="149"/>
-      <c r="B66" s="150"/>
+      <c r="A66" s="160"/>
+      <c r="B66" s="161"/>
       <c r="C66" s="120">
         <f t="shared" si="10"/>
         <v>62</v>
@@ -9507,7 +9481,7 @@
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="K66" s="151"/>
+      <c r="K66" s="162"/>
       <c r="L66" s="124">
         <v>8</v>
       </c>
@@ -9567,8 +9541,8 @@
       <c r="AW66" s="136"/>
     </row>
     <row r="67" spans="1:49" s="125" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A67" s="149"/>
-      <c r="B67" s="150"/>
+      <c r="A67" s="160"/>
+      <c r="B67" s="161"/>
       <c r="C67" s="120">
         <f t="shared" si="10"/>
         <v>64</v>
@@ -9596,7 +9570,7 @@
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="K67" s="151"/>
+      <c r="K67" s="162"/>
       <c r="L67" s="124">
         <v>6</v>
       </c>
@@ -9656,10 +9630,10 @@
       <c r="AW67" s="136"/>
     </row>
     <row r="68" spans="1:49" s="129" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A68" s="152">
+      <c r="A68" s="163">
         <v>1536</v>
       </c>
-      <c r="B68" s="152">
+      <c r="B68" s="163">
         <v>7071</v>
       </c>
       <c r="C68" s="120">
@@ -9687,7 +9661,7 @@
         <f t="shared" si="0"/>
         <v>300</v>
       </c>
-      <c r="K68" s="152">
+      <c r="K68" s="163">
         <f>SUM(J68:J82)</f>
         <v>1896</v>
       </c>
@@ -9750,8 +9724,8 @@
       <c r="AW68" s="137"/>
     </row>
     <row r="69" spans="1:49" s="129" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A69" s="153"/>
-      <c r="B69" s="153"/>
+      <c r="A69" s="164"/>
+      <c r="B69" s="164"/>
       <c r="C69" s="120">
         <f t="shared" ref="C69:C82" si="12">E68+1</f>
         <v>51</v>
@@ -9779,7 +9753,7 @@
         <f t="shared" si="0"/>
         <v>120</v>
       </c>
-      <c r="K69" s="153"/>
+      <c r="K69" s="164"/>
       <c r="L69" s="124">
         <v>5</v>
       </c>
@@ -9839,8 +9813,8 @@
       <c r="AW69" s="137"/>
     </row>
     <row r="70" spans="1:49" s="129" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A70" s="153"/>
-      <c r="B70" s="153"/>
+      <c r="A70" s="164"/>
+      <c r="B70" s="164"/>
       <c r="C70" s="120">
         <f t="shared" si="12"/>
         <v>71</v>
@@ -9868,7 +9842,7 @@
         <f t="shared" si="0"/>
         <v>120</v>
       </c>
-      <c r="K70" s="153"/>
+      <c r="K70" s="164"/>
       <c r="L70" s="124">
         <v>5</v>
       </c>
@@ -9928,8 +9902,8 @@
       <c r="AW70" s="137"/>
     </row>
     <row r="71" spans="1:49" s="129" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A71" s="153"/>
-      <c r="B71" s="153"/>
+      <c r="A71" s="164"/>
+      <c r="B71" s="164"/>
       <c r="C71" s="120">
         <f t="shared" si="12"/>
         <v>91</v>
@@ -9957,7 +9931,7 @@
         <f t="shared" si="0"/>
         <v>180</v>
       </c>
-      <c r="K71" s="153"/>
+      <c r="K71" s="164"/>
       <c r="L71" s="124">
         <v>5</v>
       </c>
@@ -10017,8 +9991,8 @@
       <c r="AW71" s="137"/>
     </row>
     <row r="72" spans="1:49" s="129" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A72" s="153"/>
-      <c r="B72" s="153"/>
+      <c r="A72" s="164"/>
+      <c r="B72" s="164"/>
       <c r="C72" s="120">
         <f t="shared" si="12"/>
         <v>121</v>
@@ -10046,7 +10020,7 @@
         <f t="shared" si="0"/>
         <v>48</v>
       </c>
-      <c r="K72" s="153"/>
+      <c r="K72" s="164"/>
       <c r="L72" s="124">
         <v>5</v>
       </c>
@@ -10106,8 +10080,8 @@
       <c r="AW72" s="137"/>
     </row>
     <row r="73" spans="1:49" s="129" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A73" s="153"/>
-      <c r="B73" s="153"/>
+      <c r="A73" s="164"/>
+      <c r="B73" s="164"/>
       <c r="C73" s="120">
         <f t="shared" si="12"/>
         <v>129</v>
@@ -10135,7 +10109,7 @@
         <f t="shared" si="0"/>
         <v>60</v>
       </c>
-      <c r="K73" s="153"/>
+      <c r="K73" s="164"/>
       <c r="L73" s="124">
         <v>5</v>
       </c>
@@ -10195,8 +10169,8 @@
       <c r="AW73" s="137"/>
     </row>
     <row r="74" spans="1:49" s="129" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A74" s="153"/>
-      <c r="B74" s="153"/>
+      <c r="A74" s="164"/>
+      <c r="B74" s="164"/>
       <c r="C74" s="120">
         <f t="shared" si="12"/>
         <v>139</v>
@@ -10224,7 +10198,7 @@
         <f t="shared" si="0"/>
         <v>240</v>
       </c>
-      <c r="K74" s="153"/>
+      <c r="K74" s="164"/>
       <c r="L74" s="124">
         <v>5</v>
       </c>
@@ -10284,8 +10258,8 @@
       <c r="AW74" s="137"/>
     </row>
     <row r="75" spans="1:49" s="129" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A75" s="153"/>
-      <c r="B75" s="153"/>
+      <c r="A75" s="164"/>
+      <c r="B75" s="164"/>
       <c r="C75" s="120">
         <f t="shared" si="12"/>
         <v>179</v>
@@ -10313,7 +10287,7 @@
         <f t="shared" si="0"/>
         <v>60</v>
       </c>
-      <c r="K75" s="153"/>
+      <c r="K75" s="164"/>
       <c r="L75" s="124">
         <v>5</v>
       </c>
@@ -10373,8 +10347,8 @@
       <c r="AW75" s="137"/>
     </row>
     <row r="76" spans="1:49" s="129" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A76" s="153"/>
-      <c r="B76" s="153"/>
+      <c r="A76" s="164"/>
+      <c r="B76" s="164"/>
       <c r="C76" s="120">
         <f t="shared" si="12"/>
         <v>189</v>
@@ -10402,7 +10376,7 @@
         <f t="shared" si="0"/>
         <v>90</v>
       </c>
-      <c r="K76" s="153"/>
+      <c r="K76" s="164"/>
       <c r="L76" s="124">
         <v>5</v>
       </c>
@@ -10462,8 +10436,8 @@
       <c r="AW76" s="137"/>
     </row>
     <row r="77" spans="1:49" s="129" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A77" s="153"/>
-      <c r="B77" s="153"/>
+      <c r="A77" s="164"/>
+      <c r="B77" s="164"/>
       <c r="C77" s="120">
         <f t="shared" si="12"/>
         <v>204</v>
@@ -10491,7 +10465,7 @@
         <f t="shared" ref="J77:J82" si="14">H77*I77</f>
         <v>240</v>
       </c>
-      <c r="K77" s="153"/>
+      <c r="K77" s="164"/>
       <c r="L77" s="124">
         <v>5</v>
       </c>
@@ -10551,8 +10525,8 @@
       <c r="AW77" s="137"/>
     </row>
     <row r="78" spans="1:49" s="129" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A78" s="153"/>
-      <c r="B78" s="153"/>
+      <c r="A78" s="164"/>
+      <c r="B78" s="164"/>
       <c r="C78" s="120">
         <f t="shared" si="12"/>
         <v>244</v>
@@ -10580,7 +10554,7 @@
         <f t="shared" si="14"/>
         <v>60</v>
       </c>
-      <c r="K78" s="153"/>
+      <c r="K78" s="164"/>
       <c r="L78" s="124">
         <v>5</v>
       </c>
@@ -10640,8 +10614,8 @@
       <c r="AW78" s="137"/>
     </row>
     <row r="79" spans="1:49" s="129" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A79" s="153"/>
-      <c r="B79" s="153"/>
+      <c r="A79" s="164"/>
+      <c r="B79" s="164"/>
       <c r="C79" s="120">
         <f t="shared" si="12"/>
         <v>254</v>
@@ -10669,7 +10643,7 @@
         <f t="shared" si="14"/>
         <v>90</v>
       </c>
-      <c r="K79" s="153"/>
+      <c r="K79" s="164"/>
       <c r="L79" s="124">
         <v>5</v>
       </c>
@@ -10729,8 +10703,8 @@
       <c r="AW79" s="137"/>
     </row>
     <row r="80" spans="1:49" s="129" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A80" s="153"/>
-      <c r="B80" s="153"/>
+      <c r="A80" s="164"/>
+      <c r="B80" s="164"/>
       <c r="C80" s="120">
         <f t="shared" si="12"/>
         <v>269</v>
@@ -10758,7 +10732,7 @@
         <f t="shared" si="14"/>
         <v>180</v>
       </c>
-      <c r="K80" s="153"/>
+      <c r="K80" s="164"/>
       <c r="L80" s="124">
         <v>5</v>
       </c>
@@ -10818,8 +10792,8 @@
       <c r="AW80" s="137"/>
     </row>
     <row r="81" spans="1:49" s="129" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A81" s="153"/>
-      <c r="B81" s="153"/>
+      <c r="A81" s="164"/>
+      <c r="B81" s="164"/>
       <c r="C81" s="120">
         <f t="shared" si="12"/>
         <v>299</v>
@@ -10847,7 +10821,7 @@
         <f t="shared" si="14"/>
         <v>48</v>
       </c>
-      <c r="K81" s="153"/>
+      <c r="K81" s="164"/>
       <c r="L81" s="124">
         <v>5</v>
       </c>
@@ -10907,8 +10881,8 @@
       <c r="AW81" s="137"/>
     </row>
     <row r="82" spans="1:49" s="129" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A82" s="154"/>
-      <c r="B82" s="154"/>
+      <c r="A82" s="165"/>
+      <c r="B82" s="165"/>
       <c r="C82" s="120">
         <f t="shared" si="12"/>
         <v>307</v>
@@ -10936,7 +10910,7 @@
         <f t="shared" si="14"/>
         <v>60</v>
       </c>
-      <c r="K82" s="154"/>
+      <c r="K82" s="165"/>
       <c r="L82" s="124">
         <v>5</v>
       </c>

--- a/shipping-tool/document/範例產出檔案.xlsx
+++ b/shipping-tool/document/範例產出檔案.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\RondoFile\客戶\巨瑞國際\source\SIReport_Auto\shipping-tool\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8486B5D-D166-4AE3-8127-2C4C41DDB56F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16DF59D5-FEE4-4B23-915B-B0BE8F7C9682}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1152" yWindow="756" windowWidth="14304" windowHeight="12204" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="828" yWindow="0" windowWidth="20916" windowHeight="11556" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="SI " sheetId="35" r:id="rId1"/>
+    <sheet name="SI" sheetId="35" r:id="rId1"/>
     <sheet name="ISF Data Sheet" sheetId="36" r:id="rId2"/>
     <sheet name="PL" sheetId="56" r:id="rId3"/>
   </sheets>
@@ -2405,6 +2405,9 @@
     <xf numFmtId="0" fontId="52" fillId="3" borderId="0" xfId="37" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="6" xfId="44" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="36" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2414,15 +2417,84 @@
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="22" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="51" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="52" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="52" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="1" xfId="53" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="1" xfId="53" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="1" xfId="53" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="1" xfId="53" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="1" xfId="46" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="79" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="79" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="79" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="79" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="79" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="79" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="18" fillId="2" borderId="1" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="18" fillId="2" borderId="1" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="18" fillId="2" borderId="2" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="18" fillId="2" borderId="3" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="18" fillId="2" borderId="4" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="18" fillId="2" borderId="2" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="18" fillId="2" borderId="3" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="18" fillId="2" borderId="4" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="18" fillId="2" borderId="2" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="18" fillId="2" borderId="3" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="18" fillId="2" borderId="4" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="18" fillId="2" borderId="1" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="49" fontId="18" fillId="2" borderId="1" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="180" fontId="18" fillId="2" borderId="1" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="2" borderId="2" xfId="54" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2430,78 +2502,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="2" borderId="4" xfId="54" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="79" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="79" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="79" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="79" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="79" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="79" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="18" fillId="2" borderId="2" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="18" fillId="2" borderId="3" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="18" fillId="2" borderId="4" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="18" fillId="2" borderId="2" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="18" fillId="2" borderId="3" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="18" fillId="2" borderId="4" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="180" fontId="18" fillId="2" borderId="2" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="180" fontId="18" fillId="2" borderId="3" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="180" fontId="18" fillId="2" borderId="4" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="51" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="52" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="52" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="1" xfId="53" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="1" xfId="53" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="1" xfId="53" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="1" xfId="53" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="1" xfId="46" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="6" xfId="44" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2967,15 +2967,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" s="4" customFormat="1" ht="21">
-      <c r="A1" s="157" t="s">
+      <c r="A1" s="158" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="157"/>
-      <c r="C1" s="157"/>
-      <c r="D1" s="157"/>
-      <c r="E1" s="157"/>
-      <c r="F1" s="157"/>
-      <c r="G1" s="157"/>
+      <c r="B1" s="158"/>
+      <c r="C1" s="158"/>
+      <c r="D1" s="158"/>
+      <c r="E1" s="158"/>
+      <c r="F1" s="158"/>
+      <c r="G1" s="158"/>
       <c r="H1" s="1" t="s">
         <v>170</v>
       </c>
@@ -3556,7 +3556,7 @@
       <c r="D53" s="141" t="s">
         <v>166</v>
       </c>
-      <c r="E53" s="189" t="s">
+      <c r="E53" s="157" t="s">
         <v>171</v>
       </c>
       <c r="F53" s="34"/>
@@ -3940,10 +3940,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="17.399999999999999">
-      <c r="A1" s="158" t="s">
+      <c r="A1" s="159" t="s">
         <v>61</v>
       </c>
-      <c r="B1" s="159"/>
+      <c r="B1" s="160"/>
       <c r="M1" s="38"/>
     </row>
     <row r="3" spans="1:13" ht="15" customHeight="1">
@@ -4285,27 +4285,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:49" ht="17.399999999999999">
-      <c r="A1" s="181" t="s">
+      <c r="A1" s="161" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="181"/>
-      <c r="C1" s="181"/>
-      <c r="D1" s="181"/>
-      <c r="E1" s="181"/>
-      <c r="F1" s="181"/>
-      <c r="G1" s="181"/>
-      <c r="H1" s="181"/>
-      <c r="I1" s="181"/>
-      <c r="J1" s="181"/>
-      <c r="K1" s="181"/>
-      <c r="L1" s="181"/>
-      <c r="M1" s="181"/>
-      <c r="N1" s="181"/>
-      <c r="O1" s="181"/>
-      <c r="P1" s="181"/>
-      <c r="Q1" s="181"/>
-      <c r="R1" s="181"/>
-      <c r="S1" s="181"/>
+      <c r="B1" s="161"/>
+      <c r="C1" s="161"/>
+      <c r="D1" s="161"/>
+      <c r="E1" s="161"/>
+      <c r="F1" s="161"/>
+      <c r="G1" s="161"/>
+      <c r="H1" s="161"/>
+      <c r="I1" s="161"/>
+      <c r="J1" s="161"/>
+      <c r="K1" s="161"/>
+      <c r="L1" s="161"/>
+      <c r="M1" s="161"/>
+      <c r="N1" s="161"/>
+      <c r="O1" s="161"/>
+      <c r="P1" s="161"/>
+      <c r="Q1" s="161"/>
+      <c r="R1" s="161"/>
+      <c r="S1" s="161"/>
     </row>
     <row r="2" spans="1:49" s="98" customFormat="1" ht="13.8">
       <c r="A2" s="95" t="s">
@@ -4323,10 +4323,10 @@
       <c r="L2" s="99"/>
       <c r="M2" s="101"/>
       <c r="N2" s="99"/>
-      <c r="O2" s="182" t="s">
+      <c r="O2" s="162" t="s">
         <v>158</v>
       </c>
-      <c r="P2" s="182"/>
+      <c r="P2" s="162"/>
       <c r="Q2" s="102" t="s">
         <v>3</v>
       </c>
@@ -4415,11 +4415,11 @@
       <c r="A6" s="95" t="s">
         <v>157</v>
       </c>
-      <c r="B6" s="183"/>
-      <c r="C6" s="183"/>
-      <c r="D6" s="183"/>
-      <c r="E6" s="183"/>
-      <c r="F6" s="183"/>
+      <c r="B6" s="163"/>
+      <c r="C6" s="163"/>
+      <c r="D6" s="163"/>
+      <c r="E6" s="163"/>
+      <c r="F6" s="163"/>
       <c r="G6" s="118"/>
       <c r="I6" s="99"/>
       <c r="J6" s="100"/>
@@ -4453,70 +4453,70 @@
       <c r="S7" s="88"/>
     </row>
     <row r="8" spans="1:49" s="90" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A8" s="184" t="s">
+      <c r="A8" s="164" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="185" t="s">
+      <c r="B8" s="165" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="185" t="s">
+      <c r="C8" s="165" t="s">
         <v>11</v>
       </c>
-      <c r="D8" s="185"/>
-      <c r="E8" s="185"/>
-      <c r="F8" s="185" t="s">
+      <c r="D8" s="165"/>
+      <c r="E8" s="165"/>
+      <c r="F8" s="165" t="s">
         <v>12</v>
       </c>
-      <c r="G8" s="186" t="s">
+      <c r="G8" s="166" t="s">
         <v>13</v>
       </c>
-      <c r="H8" s="186" t="s">
+      <c r="H8" s="166" t="s">
         <v>14</v>
       </c>
-      <c r="I8" s="186" t="s">
+      <c r="I8" s="166" t="s">
         <v>15</v>
       </c>
-      <c r="J8" s="187" t="s">
+      <c r="J8" s="167" t="s">
         <v>16</v>
       </c>
-      <c r="K8" s="184" t="s">
+      <c r="K8" s="164" t="s">
         <v>17</v>
       </c>
-      <c r="L8" s="185" t="s">
+      <c r="L8" s="165" t="s">
         <v>153</v>
       </c>
-      <c r="M8" s="185"/>
-      <c r="N8" s="185"/>
-      <c r="O8" s="185"/>
-      <c r="P8" s="188" t="s">
+      <c r="M8" s="165"/>
+      <c r="N8" s="165"/>
+      <c r="O8" s="165"/>
+      <c r="P8" s="168" t="s">
         <v>18</v>
       </c>
-      <c r="Q8" s="188"/>
-      <c r="R8" s="188"/>
+      <c r="Q8" s="168"/>
+      <c r="R8" s="168"/>
       <c r="S8" s="89" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:49" s="90" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A9" s="184"/>
-      <c r="B9" s="185"/>
-      <c r="C9" s="185"/>
-      <c r="D9" s="185"/>
-      <c r="E9" s="185"/>
-      <c r="F9" s="185"/>
-      <c r="G9" s="186"/>
-      <c r="H9" s="186"/>
-      <c r="I9" s="186"/>
-      <c r="J9" s="187"/>
-      <c r="K9" s="187"/>
-      <c r="L9" s="185" t="s">
+      <c r="A9" s="164"/>
+      <c r="B9" s="165"/>
+      <c r="C9" s="165"/>
+      <c r="D9" s="165"/>
+      <c r="E9" s="165"/>
+      <c r="F9" s="165"/>
+      <c r="G9" s="166"/>
+      <c r="H9" s="166"/>
+      <c r="I9" s="166"/>
+      <c r="J9" s="167"/>
+      <c r="K9" s="167"/>
+      <c r="L9" s="165" t="s">
         <v>20</v>
       </c>
-      <c r="M9" s="185"/>
-      <c r="N9" s="185" t="s">
+      <c r="M9" s="165"/>
+      <c r="N9" s="165" t="s">
         <v>21</v>
       </c>
-      <c r="O9" s="185"/>
+      <c r="O9" s="165"/>
       <c r="P9" s="91" t="s">
         <v>22</v>
       </c>
@@ -4531,10 +4531,10 @@
       </c>
     </row>
     <row r="10" spans="1:49" s="115" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A10" s="166" t="s">
+      <c r="A10" s="169" t="s">
         <v>150</v>
       </c>
-      <c r="B10" s="168" t="s">
+      <c r="B10" s="171" t="s">
         <v>151</v>
       </c>
       <c r="C10" s="109">
@@ -4562,7 +4562,7 @@
         <f>SUM(H10*I10)</f>
         <v>180</v>
       </c>
-      <c r="K10" s="170">
+      <c r="K10" s="173">
         <f>SUM(J10:J12)</f>
         <v>660</v>
       </c>
@@ -4595,8 +4595,8 @@
       </c>
     </row>
     <row r="11" spans="1:49" s="115" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A11" s="167"/>
-      <c r="B11" s="169"/>
+      <c r="A11" s="170"/>
+      <c r="B11" s="172"/>
       <c r="C11" s="109">
         <v>31</v>
       </c>
@@ -4622,7 +4622,7 @@
         <f>SUM(H11*I11)</f>
         <v>240</v>
       </c>
-      <c r="K11" s="171"/>
+      <c r="K11" s="174"/>
       <c r="L11" s="113">
         <v>4.5999999999999996</v>
       </c>
@@ -4652,8 +4652,8 @@
       </c>
     </row>
     <row r="12" spans="1:49" s="115" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A12" s="167"/>
-      <c r="B12" s="169"/>
+      <c r="A12" s="170"/>
+      <c r="B12" s="172"/>
       <c r="C12" s="109">
         <v>71</v>
       </c>
@@ -4679,7 +4679,7 @@
         <f>SUM(H12*I12)</f>
         <v>240</v>
       </c>
-      <c r="K12" s="171"/>
+      <c r="K12" s="174"/>
       <c r="L12" s="113">
         <v>4.5999999999999996</v>
       </c>
@@ -4709,10 +4709,10 @@
       </c>
     </row>
     <row r="13" spans="1:49" s="125" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A13" s="172" t="s">
+      <c r="A13" s="177" t="s">
         <v>111</v>
       </c>
-      <c r="B13" s="175" t="s">
+      <c r="B13" s="180" t="s">
         <v>127</v>
       </c>
       <c r="C13" s="120">
@@ -4740,7 +4740,7 @@
         <f t="shared" ref="J13:J76" si="0">H13*I13</f>
         <v>420</v>
       </c>
-      <c r="K13" s="178">
+      <c r="K13" s="183">
         <f>SUM(J13:J16)</f>
         <v>1500</v>
       </c>
@@ -4803,8 +4803,8 @@
       <c r="AW13" s="136"/>
     </row>
     <row r="14" spans="1:49" s="125" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A14" s="173"/>
-      <c r="B14" s="176"/>
+      <c r="A14" s="178"/>
+      <c r="B14" s="181"/>
       <c r="C14" s="120">
         <f t="shared" ref="C14:C18" si="4">E13+1</f>
         <v>269</v>
@@ -4832,7 +4832,7 @@
         <f t="shared" si="0"/>
         <v>600</v>
       </c>
-      <c r="K14" s="179"/>
+      <c r="K14" s="184"/>
       <c r="L14" s="124">
         <v>9</v>
       </c>
@@ -4892,8 +4892,8 @@
       <c r="AW14" s="136"/>
     </row>
     <row r="15" spans="1:49" s="125" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A15" s="173"/>
-      <c r="B15" s="176"/>
+      <c r="A15" s="178"/>
+      <c r="B15" s="181"/>
       <c r="C15" s="120">
         <v>424</v>
       </c>
@@ -4919,7 +4919,7 @@
         <f t="shared" si="0"/>
         <v>180</v>
       </c>
-      <c r="K15" s="179"/>
+      <c r="K15" s="184"/>
       <c r="L15" s="124">
         <v>9</v>
       </c>
@@ -4979,8 +4979,8 @@
       <c r="AW15" s="136"/>
     </row>
     <row r="16" spans="1:49" s="125" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A16" s="174"/>
-      <c r="B16" s="177"/>
+      <c r="A16" s="179"/>
+      <c r="B16" s="182"/>
       <c r="C16" s="120">
         <f t="shared" si="4"/>
         <v>439</v>
@@ -5008,7 +5008,7 @@
         <f t="shared" si="0"/>
         <v>300</v>
       </c>
-      <c r="K16" s="180"/>
+      <c r="K16" s="185"/>
       <c r="L16" s="124">
         <v>9</v>
       </c>
@@ -5068,10 +5068,10 @@
       <c r="AW16" s="136"/>
     </row>
     <row r="17" spans="1:49" s="125" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A17" s="172" t="s">
+      <c r="A17" s="177" t="s">
         <v>112</v>
       </c>
-      <c r="B17" s="175" t="s">
+      <c r="B17" s="180" t="s">
         <v>130</v>
       </c>
       <c r="C17" s="120">
@@ -5099,7 +5099,7 @@
         <f t="shared" si="0"/>
         <v>240</v>
       </c>
-      <c r="K17" s="178">
+      <c r="K17" s="183">
         <f>SUM(J17:J21)</f>
         <v>1416</v>
       </c>
@@ -5162,8 +5162,8 @@
       <c r="AW17" s="136"/>
     </row>
     <row r="18" spans="1:49" s="125" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A18" s="173"/>
-      <c r="B18" s="176"/>
+      <c r="A18" s="178"/>
+      <c r="B18" s="181"/>
       <c r="C18" s="120">
         <f t="shared" si="4"/>
         <v>106</v>
@@ -5191,7 +5191,7 @@
         <f t="shared" si="0"/>
         <v>360</v>
       </c>
-      <c r="K18" s="179"/>
+      <c r="K18" s="184"/>
       <c r="L18" s="124">
         <v>9</v>
       </c>
@@ -5251,8 +5251,8 @@
       <c r="AW18" s="136"/>
     </row>
     <row r="19" spans="1:49" s="125" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A19" s="173"/>
-      <c r="B19" s="176"/>
+      <c r="A19" s="178"/>
+      <c r="B19" s="181"/>
       <c r="C19" s="120">
         <v>136</v>
       </c>
@@ -5278,7 +5278,7 @@
         <f t="shared" si="0"/>
         <v>96</v>
       </c>
-      <c r="K19" s="179"/>
+      <c r="K19" s="184"/>
       <c r="L19" s="124">
         <v>9</v>
       </c>
@@ -5338,8 +5338,8 @@
       <c r="AW19" s="136"/>
     </row>
     <row r="20" spans="1:49" s="125" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A20" s="173"/>
-      <c r="B20" s="176"/>
+      <c r="A20" s="178"/>
+      <c r="B20" s="181"/>
       <c r="C20" s="120">
         <f t="shared" ref="C20:C24" si="6">E19+1</f>
         <v>144</v>
@@ -5367,7 +5367,7 @@
         <f t="shared" si="0"/>
         <v>300</v>
       </c>
-      <c r="K20" s="179"/>
+      <c r="K20" s="184"/>
       <c r="L20" s="124">
         <v>9</v>
       </c>
@@ -5427,8 +5427,8 @@
       <c r="AW20" s="136"/>
     </row>
     <row r="21" spans="1:49" s="125" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A21" s="174"/>
-      <c r="B21" s="177"/>
+      <c r="A21" s="179"/>
+      <c r="B21" s="182"/>
       <c r="C21" s="120">
         <f t="shared" si="6"/>
         <v>169</v>
@@ -5456,7 +5456,7 @@
         <f t="shared" si="0"/>
         <v>420</v>
       </c>
-      <c r="K21" s="180"/>
+      <c r="K21" s="185"/>
       <c r="L21" s="124">
         <v>9</v>
       </c>
@@ -5516,10 +5516,10 @@
       <c r="AW21" s="136"/>
     </row>
     <row r="22" spans="1:49" s="125" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A22" s="160" t="s">
+      <c r="A22" s="186" t="s">
         <v>122</v>
       </c>
-      <c r="B22" s="161" t="s">
+      <c r="B22" s="175" t="s">
         <v>133</v>
       </c>
       <c r="C22" s="120">
@@ -5547,7 +5547,7 @@
         <f t="shared" si="0"/>
         <v>120</v>
       </c>
-      <c r="K22" s="162">
+      <c r="K22" s="176">
         <f>SUM(J22:J24)</f>
         <v>210</v>
       </c>
@@ -5610,8 +5610,8 @@
       <c r="AW22" s="136"/>
     </row>
     <row r="23" spans="1:49" s="125" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A23" s="160"/>
-      <c r="B23" s="161"/>
+      <c r="A23" s="186"/>
+      <c r="B23" s="175"/>
       <c r="C23" s="120">
         <f t="shared" si="6"/>
         <v>21</v>
@@ -5639,7 +5639,7 @@
         <f t="shared" si="0"/>
         <v>60</v>
       </c>
-      <c r="K23" s="162"/>
+      <c r="K23" s="176"/>
       <c r="L23" s="124">
         <v>4.3</v>
       </c>
@@ -5699,8 +5699,8 @@
       <c r="AW23" s="136"/>
     </row>
     <row r="24" spans="1:49" s="125" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A24" s="160"/>
-      <c r="B24" s="161"/>
+      <c r="A24" s="186"/>
+      <c r="B24" s="175"/>
       <c r="C24" s="120">
         <f t="shared" si="6"/>
         <v>31</v>
@@ -5728,7 +5728,7 @@
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="K24" s="162"/>
+      <c r="K24" s="176"/>
       <c r="L24" s="124">
         <v>4.3</v>
       </c>
@@ -5788,10 +5788,10 @@
       <c r="AW24" s="136"/>
     </row>
     <row r="25" spans="1:49" s="125" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A25" s="160" t="s">
+      <c r="A25" s="186" t="s">
         <v>123</v>
       </c>
-      <c r="B25" s="161" t="s">
+      <c r="B25" s="175" t="s">
         <v>124</v>
       </c>
       <c r="C25" s="120">
@@ -5819,7 +5819,7 @@
         <f t="shared" si="0"/>
         <v>210</v>
       </c>
-      <c r="K25" s="162">
+      <c r="K25" s="176">
         <f>SUM(J25:J27)</f>
         <v>330</v>
       </c>
@@ -5882,8 +5882,8 @@
       <c r="AW25" s="136"/>
     </row>
     <row r="26" spans="1:49" s="125" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A26" s="160"/>
-      <c r="B26" s="161"/>
+      <c r="A26" s="186"/>
+      <c r="B26" s="175"/>
       <c r="C26" s="120">
         <f t="shared" ref="C26:C30" si="8">E25+1</f>
         <v>36</v>
@@ -5911,7 +5911,7 @@
         <f t="shared" si="0"/>
         <v>60</v>
       </c>
-      <c r="K26" s="162"/>
+      <c r="K26" s="176"/>
       <c r="L26" s="124">
         <v>5</v>
       </c>
@@ -5971,8 +5971,8 @@
       <c r="AW26" s="136"/>
     </row>
     <row r="27" spans="1:49" s="125" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A27" s="160"/>
-      <c r="B27" s="161"/>
+      <c r="A27" s="186"/>
+      <c r="B27" s="175"/>
       <c r="C27" s="120">
         <f t="shared" si="8"/>
         <v>46</v>
@@ -6000,7 +6000,7 @@
         <f t="shared" si="0"/>
         <v>60</v>
       </c>
-      <c r="K27" s="162"/>
+      <c r="K27" s="176"/>
       <c r="L27" s="124">
         <v>5</v>
       </c>
@@ -6060,10 +6060,10 @@
       <c r="AW27" s="136"/>
     </row>
     <row r="28" spans="1:49" s="125" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A28" s="160" t="s">
+      <c r="A28" s="186" t="s">
         <v>125</v>
       </c>
-      <c r="B28" s="161" t="s">
+      <c r="B28" s="175" t="s">
         <v>124</v>
       </c>
       <c r="C28" s="120">
@@ -6091,7 +6091,7 @@
         <f t="shared" si="0"/>
         <v>300</v>
       </c>
-      <c r="K28" s="162">
+      <c r="K28" s="176">
         <f>SUM(J28:J30)</f>
         <v>420</v>
       </c>
@@ -6154,8 +6154,8 @@
       <c r="AW28" s="136"/>
     </row>
     <row r="29" spans="1:49" s="125" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A29" s="160"/>
-      <c r="B29" s="161"/>
+      <c r="A29" s="186"/>
+      <c r="B29" s="175"/>
       <c r="C29" s="120">
         <f t="shared" si="8"/>
         <v>51</v>
@@ -6183,7 +6183,7 @@
         <f t="shared" si="0"/>
         <v>60</v>
       </c>
-      <c r="K29" s="162"/>
+      <c r="K29" s="176"/>
       <c r="L29" s="124">
         <v>5</v>
       </c>
@@ -6243,8 +6243,8 @@
       <c r="AW29" s="136"/>
     </row>
     <row r="30" spans="1:49" s="125" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A30" s="160"/>
-      <c r="B30" s="161"/>
+      <c r="A30" s="186"/>
+      <c r="B30" s="175"/>
       <c r="C30" s="120">
         <f t="shared" si="8"/>
         <v>61</v>
@@ -6272,7 +6272,7 @@
         <f t="shared" si="0"/>
         <v>60</v>
       </c>
-      <c r="K30" s="162"/>
+      <c r="K30" s="176"/>
       <c r="L30" s="124">
         <v>5</v>
       </c>
@@ -6332,10 +6332,10 @@
       <c r="AW30" s="136"/>
     </row>
     <row r="31" spans="1:49" s="125" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A31" s="160" t="s">
+      <c r="A31" s="186" t="s">
         <v>138</v>
       </c>
-      <c r="B31" s="161" t="s">
+      <c r="B31" s="175" t="s">
         <v>126</v>
       </c>
       <c r="C31" s="120">
@@ -6363,7 +6363,7 @@
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="K31" s="162">
+      <c r="K31" s="176">
         <f>SUM(J31:J67)</f>
         <v>687</v>
       </c>
@@ -6426,8 +6426,8 @@
       <c r="AW31" s="136"/>
     </row>
     <row r="32" spans="1:49" s="125" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A32" s="160"/>
-      <c r="B32" s="161"/>
+      <c r="A32" s="186"/>
+      <c r="B32" s="175"/>
       <c r="C32" s="120">
         <f t="shared" ref="C32:C67" si="10">E31+1</f>
         <v>2</v>
@@ -6455,7 +6455,7 @@
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="K32" s="162"/>
+      <c r="K32" s="176"/>
       <c r="L32" s="124">
         <v>6</v>
       </c>
@@ -6515,8 +6515,8 @@
       <c r="AW32" s="136"/>
     </row>
     <row r="33" spans="1:49" s="125" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A33" s="160"/>
-      <c r="B33" s="161"/>
+      <c r="A33" s="186"/>
+      <c r="B33" s="175"/>
       <c r="C33" s="120">
         <f t="shared" si="10"/>
         <v>3</v>
@@ -6544,7 +6544,7 @@
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="K33" s="162"/>
+      <c r="K33" s="176"/>
       <c r="L33" s="124">
         <v>6</v>
       </c>
@@ -6604,8 +6604,8 @@
       <c r="AW33" s="136"/>
     </row>
     <row r="34" spans="1:49" s="125" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A34" s="160"/>
-      <c r="B34" s="161"/>
+      <c r="A34" s="186"/>
+      <c r="B34" s="175"/>
       <c r="C34" s="120">
         <f t="shared" si="10"/>
         <v>4</v>
@@ -6633,7 +6633,7 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="K34" s="162"/>
+      <c r="K34" s="176"/>
       <c r="L34" s="124">
         <v>4</v>
       </c>
@@ -6693,8 +6693,8 @@
       <c r="AW34" s="136"/>
     </row>
     <row r="35" spans="1:49" s="125" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A35" s="160"/>
-      <c r="B35" s="161"/>
+      <c r="A35" s="186"/>
+      <c r="B35" s="175"/>
       <c r="C35" s="120">
         <f t="shared" si="10"/>
         <v>5</v>
@@ -6722,7 +6722,7 @@
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="K35" s="162"/>
+      <c r="K35" s="176"/>
       <c r="L35" s="124">
         <v>6</v>
       </c>
@@ -6782,8 +6782,8 @@
       <c r="AW35" s="136"/>
     </row>
     <row r="36" spans="1:49" s="125" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A36" s="160"/>
-      <c r="B36" s="161"/>
+      <c r="A36" s="186"/>
+      <c r="B36" s="175"/>
       <c r="C36" s="120">
         <f t="shared" si="10"/>
         <v>7</v>
@@ -6811,7 +6811,7 @@
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="K36" s="162"/>
+      <c r="K36" s="176"/>
       <c r="L36" s="124">
         <v>8</v>
       </c>
@@ -6871,8 +6871,8 @@
       <c r="AW36" s="136"/>
     </row>
     <row r="37" spans="1:49" s="125" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A37" s="160"/>
-      <c r="B37" s="161"/>
+      <c r="A37" s="186"/>
+      <c r="B37" s="175"/>
       <c r="C37" s="120">
         <f t="shared" si="10"/>
         <v>9</v>
@@ -6900,7 +6900,7 @@
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="K37" s="162"/>
+      <c r="K37" s="176"/>
       <c r="L37" s="124">
         <v>6</v>
       </c>
@@ -6960,8 +6960,8 @@
       <c r="AW37" s="136"/>
     </row>
     <row r="38" spans="1:49" s="125" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A38" s="160"/>
-      <c r="B38" s="161"/>
+      <c r="A38" s="186"/>
+      <c r="B38" s="175"/>
       <c r="C38" s="120">
         <f t="shared" si="10"/>
         <v>11</v>
@@ -6989,7 +6989,7 @@
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="K38" s="162"/>
+      <c r="K38" s="176"/>
       <c r="L38" s="124">
         <v>8</v>
       </c>
@@ -7049,8 +7049,8 @@
       <c r="AW38" s="136"/>
     </row>
     <row r="39" spans="1:49" s="125" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A39" s="160"/>
-      <c r="B39" s="161"/>
+      <c r="A39" s="186"/>
+      <c r="B39" s="175"/>
       <c r="C39" s="120">
         <f t="shared" si="10"/>
         <v>14</v>
@@ -7078,7 +7078,7 @@
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="K39" s="162"/>
+      <c r="K39" s="176"/>
       <c r="L39" s="124">
         <v>8</v>
       </c>
@@ -7138,8 +7138,8 @@
       <c r="AW39" s="136"/>
     </row>
     <row r="40" spans="1:49" s="125" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A40" s="160"/>
-      <c r="B40" s="161"/>
+      <c r="A40" s="186"/>
+      <c r="B40" s="175"/>
       <c r="C40" s="120">
         <f t="shared" si="10"/>
         <v>16</v>
@@ -7167,7 +7167,7 @@
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="K40" s="162"/>
+      <c r="K40" s="176"/>
       <c r="L40" s="124">
         <v>8</v>
       </c>
@@ -7227,8 +7227,8 @@
       <c r="AW40" s="136"/>
     </row>
     <row r="41" spans="1:49" s="125" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A41" s="160"/>
-      <c r="B41" s="161"/>
+      <c r="A41" s="186"/>
+      <c r="B41" s="175"/>
       <c r="C41" s="120">
         <f t="shared" si="10"/>
         <v>19</v>
@@ -7256,7 +7256,7 @@
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="K41" s="162"/>
+      <c r="K41" s="176"/>
       <c r="L41" s="124">
         <v>8</v>
       </c>
@@ -7316,8 +7316,8 @@
       <c r="AW41" s="136"/>
     </row>
     <row r="42" spans="1:49" s="125" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A42" s="160"/>
-      <c r="B42" s="161"/>
+      <c r="A42" s="186"/>
+      <c r="B42" s="175"/>
       <c r="C42" s="120">
         <f t="shared" si="10"/>
         <v>22</v>
@@ -7345,7 +7345,7 @@
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="K42" s="162"/>
+      <c r="K42" s="176"/>
       <c r="L42" s="124">
         <v>8</v>
       </c>
@@ -7405,8 +7405,8 @@
       <c r="AW42" s="136"/>
     </row>
     <row r="43" spans="1:49" s="125" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A43" s="160"/>
-      <c r="B43" s="161"/>
+      <c r="A43" s="186"/>
+      <c r="B43" s="175"/>
       <c r="C43" s="120">
         <f t="shared" si="10"/>
         <v>24</v>
@@ -7434,7 +7434,7 @@
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="K43" s="162"/>
+      <c r="K43" s="176"/>
       <c r="L43" s="124">
         <v>8</v>
       </c>
@@ -7494,8 +7494,8 @@
       <c r="AW43" s="136"/>
     </row>
     <row r="44" spans="1:49" s="125" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A44" s="160"/>
-      <c r="B44" s="161"/>
+      <c r="A44" s="186"/>
+      <c r="B44" s="175"/>
       <c r="C44" s="120">
         <f t="shared" si="10"/>
         <v>25</v>
@@ -7523,7 +7523,7 @@
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="K44" s="162"/>
+      <c r="K44" s="176"/>
       <c r="L44" s="124">
         <v>6</v>
       </c>
@@ -7583,8 +7583,8 @@
       <c r="AW44" s="136"/>
     </row>
     <row r="45" spans="1:49" s="125" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A45" s="160"/>
-      <c r="B45" s="161"/>
+      <c r="A45" s="186"/>
+      <c r="B45" s="175"/>
       <c r="C45" s="120">
         <f t="shared" si="10"/>
         <v>26</v>
@@ -7612,7 +7612,7 @@
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="K45" s="162"/>
+      <c r="K45" s="176"/>
       <c r="L45" s="124">
         <v>6</v>
       </c>
@@ -7672,8 +7672,8 @@
       <c r="AW45" s="136"/>
     </row>
     <row r="46" spans="1:49" s="125" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A46" s="160"/>
-      <c r="B46" s="161"/>
+      <c r="A46" s="186"/>
+      <c r="B46" s="175"/>
       <c r="C46" s="120">
         <f t="shared" si="10"/>
         <v>27</v>
@@ -7701,7 +7701,7 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="K46" s="162"/>
+      <c r="K46" s="176"/>
       <c r="L46" s="124">
         <v>4</v>
       </c>
@@ -7761,8 +7761,8 @@
       <c r="AW46" s="136"/>
     </row>
     <row r="47" spans="1:49" s="125" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A47" s="160"/>
-      <c r="B47" s="161"/>
+      <c r="A47" s="186"/>
+      <c r="B47" s="175"/>
       <c r="C47" s="120">
         <f t="shared" si="10"/>
         <v>28</v>
@@ -7790,7 +7790,7 @@
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="K47" s="162"/>
+      <c r="K47" s="176"/>
       <c r="L47" s="124">
         <v>6</v>
       </c>
@@ -7850,8 +7850,8 @@
       <c r="AW47" s="136"/>
     </row>
     <row r="48" spans="1:49" s="125" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A48" s="160"/>
-      <c r="B48" s="161"/>
+      <c r="A48" s="186"/>
+      <c r="B48" s="175"/>
       <c r="C48" s="120">
         <f t="shared" si="10"/>
         <v>30</v>
@@ -7879,7 +7879,7 @@
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="K48" s="162"/>
+      <c r="K48" s="176"/>
       <c r="L48" s="124">
         <v>8</v>
       </c>
@@ -7939,8 +7939,8 @@
       <c r="AW48" s="136"/>
     </row>
     <row r="49" spans="1:49" s="125" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A49" s="160"/>
-      <c r="B49" s="161"/>
+      <c r="A49" s="186"/>
+      <c r="B49" s="175"/>
       <c r="C49" s="120">
         <f t="shared" si="10"/>
         <v>32</v>
@@ -7968,7 +7968,7 @@
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="K49" s="162"/>
+      <c r="K49" s="176"/>
       <c r="L49" s="124">
         <v>6</v>
       </c>
@@ -8028,8 +8028,8 @@
       <c r="AW49" s="136"/>
     </row>
     <row r="50" spans="1:49" s="125" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A50" s="160"/>
-      <c r="B50" s="161"/>
+      <c r="A50" s="186"/>
+      <c r="B50" s="175"/>
       <c r="C50" s="120">
         <f t="shared" si="10"/>
         <v>34</v>
@@ -8057,7 +8057,7 @@
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="K50" s="162"/>
+      <c r="K50" s="176"/>
       <c r="L50" s="124">
         <v>8</v>
       </c>
@@ -8117,8 +8117,8 @@
       <c r="AW50" s="136"/>
     </row>
     <row r="51" spans="1:49" s="125" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A51" s="160"/>
-      <c r="B51" s="161"/>
+      <c r="A51" s="186"/>
+      <c r="B51" s="175"/>
       <c r="C51" s="120">
         <f t="shared" si="10"/>
         <v>37</v>
@@ -8146,7 +8146,7 @@
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="K51" s="162"/>
+      <c r="K51" s="176"/>
       <c r="L51" s="124">
         <v>8</v>
       </c>
@@ -8206,8 +8206,8 @@
       <c r="AW51" s="136"/>
     </row>
     <row r="52" spans="1:49" s="125" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A52" s="160"/>
-      <c r="B52" s="161"/>
+      <c r="A52" s="186"/>
+      <c r="B52" s="175"/>
       <c r="C52" s="120">
         <f t="shared" si="10"/>
         <v>39</v>
@@ -8235,7 +8235,7 @@
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="K52" s="162"/>
+      <c r="K52" s="176"/>
       <c r="L52" s="124">
         <v>8</v>
       </c>
@@ -8295,8 +8295,8 @@
       <c r="AW52" s="136"/>
     </row>
     <row r="53" spans="1:49" s="125" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A53" s="160"/>
-      <c r="B53" s="161"/>
+      <c r="A53" s="186"/>
+      <c r="B53" s="175"/>
       <c r="C53" s="120">
         <f t="shared" si="10"/>
         <v>42</v>
@@ -8324,7 +8324,7 @@
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="K53" s="162"/>
+      <c r="K53" s="176"/>
       <c r="L53" s="124">
         <v>8</v>
       </c>
@@ -8384,8 +8384,8 @@
       <c r="AW53" s="136"/>
     </row>
     <row r="54" spans="1:49" s="125" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A54" s="160"/>
-      <c r="B54" s="161"/>
+      <c r="A54" s="186"/>
+      <c r="B54" s="175"/>
       <c r="C54" s="120">
         <f t="shared" si="10"/>
         <v>45</v>
@@ -8413,7 +8413,7 @@
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="K54" s="162"/>
+      <c r="K54" s="176"/>
       <c r="L54" s="124">
         <v>8</v>
       </c>
@@ -8473,8 +8473,8 @@
       <c r="AW54" s="136"/>
     </row>
     <row r="55" spans="1:49" s="125" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A55" s="160"/>
-      <c r="B55" s="161"/>
+      <c r="A55" s="186"/>
+      <c r="B55" s="175"/>
       <c r="C55" s="120">
         <f t="shared" si="10"/>
         <v>47</v>
@@ -8502,7 +8502,7 @@
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="K55" s="162"/>
+      <c r="K55" s="176"/>
       <c r="L55" s="124">
         <v>6</v>
       </c>
@@ -8562,8 +8562,8 @@
       <c r="AW55" s="136"/>
     </row>
     <row r="56" spans="1:49" s="125" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A56" s="160"/>
-      <c r="B56" s="161"/>
+      <c r="A56" s="186"/>
+      <c r="B56" s="175"/>
       <c r="C56" s="120">
         <f t="shared" si="10"/>
         <v>48</v>
@@ -8591,7 +8591,7 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="K56" s="162"/>
+      <c r="K56" s="176"/>
       <c r="L56" s="124">
         <v>4</v>
       </c>
@@ -8651,8 +8651,8 @@
       <c r="AW56" s="136"/>
     </row>
     <row r="57" spans="1:49" s="125" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A57" s="160"/>
-      <c r="B57" s="161"/>
+      <c r="A57" s="186"/>
+      <c r="B57" s="175"/>
       <c r="C57" s="120">
         <f t="shared" si="10"/>
         <v>49</v>
@@ -8680,7 +8680,7 @@
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="K57" s="162"/>
+      <c r="K57" s="176"/>
       <c r="L57" s="124">
         <v>8</v>
       </c>
@@ -8740,8 +8740,8 @@
       <c r="AW57" s="136"/>
     </row>
     <row r="58" spans="1:49" s="125" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A58" s="160"/>
-      <c r="B58" s="161"/>
+      <c r="A58" s="186"/>
+      <c r="B58" s="175"/>
       <c r="C58" s="120">
         <f t="shared" si="10"/>
         <v>50</v>
@@ -8769,7 +8769,7 @@
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="K58" s="162"/>
+      <c r="K58" s="176"/>
       <c r="L58" s="124">
         <v>6</v>
       </c>
@@ -8829,8 +8829,8 @@
       <c r="AW58" s="136"/>
     </row>
     <row r="59" spans="1:49" s="125" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A59" s="160"/>
-      <c r="B59" s="161"/>
+      <c r="A59" s="186"/>
+      <c r="B59" s="175"/>
       <c r="C59" s="120">
         <f t="shared" si="10"/>
         <v>51</v>
@@ -8858,7 +8858,7 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="K59" s="162"/>
+      <c r="K59" s="176"/>
       <c r="L59" s="124">
         <v>4</v>
       </c>
@@ -8918,8 +8918,8 @@
       <c r="AW59" s="136"/>
     </row>
     <row r="60" spans="1:49" s="125" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A60" s="160"/>
-      <c r="B60" s="161"/>
+      <c r="A60" s="186"/>
+      <c r="B60" s="175"/>
       <c r="C60" s="120">
         <f t="shared" si="10"/>
         <v>52</v>
@@ -8947,7 +8947,7 @@
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="K60" s="162"/>
+      <c r="K60" s="176"/>
       <c r="L60" s="124">
         <v>6</v>
       </c>
@@ -9007,8 +9007,8 @@
       <c r="AW60" s="136"/>
     </row>
     <row r="61" spans="1:49" s="125" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A61" s="160"/>
-      <c r="B61" s="161"/>
+      <c r="A61" s="186"/>
+      <c r="B61" s="175"/>
       <c r="C61" s="120">
         <f t="shared" si="10"/>
         <v>54</v>
@@ -9036,7 +9036,7 @@
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="K61" s="162"/>
+      <c r="K61" s="176"/>
       <c r="L61" s="124">
         <v>6</v>
       </c>
@@ -9096,8 +9096,8 @@
       <c r="AW61" s="136"/>
     </row>
     <row r="62" spans="1:49" s="125" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A62" s="160"/>
-      <c r="B62" s="161"/>
+      <c r="A62" s="186"/>
+      <c r="B62" s="175"/>
       <c r="C62" s="120">
         <f t="shared" si="10"/>
         <v>55</v>
@@ -9125,7 +9125,7 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="K62" s="162"/>
+      <c r="K62" s="176"/>
       <c r="L62" s="124">
         <v>4</v>
       </c>
@@ -9185,8 +9185,8 @@
       <c r="AW62" s="136"/>
     </row>
     <row r="63" spans="1:49" s="125" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A63" s="160"/>
-      <c r="B63" s="161"/>
+      <c r="A63" s="186"/>
+      <c r="B63" s="175"/>
       <c r="C63" s="120">
         <f t="shared" si="10"/>
         <v>56</v>
@@ -9214,7 +9214,7 @@
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="K63" s="162"/>
+      <c r="K63" s="176"/>
       <c r="L63" s="124">
         <v>8</v>
       </c>
@@ -9274,8 +9274,8 @@
       <c r="AW63" s="136"/>
     </row>
     <row r="64" spans="1:49" s="125" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A64" s="160"/>
-      <c r="B64" s="161"/>
+      <c r="A64" s="186"/>
+      <c r="B64" s="175"/>
       <c r="C64" s="120">
         <f t="shared" si="10"/>
         <v>58</v>
@@ -9303,7 +9303,7 @@
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="K64" s="162"/>
+      <c r="K64" s="176"/>
       <c r="L64" s="124">
         <v>6</v>
       </c>
@@ -9363,8 +9363,8 @@
       <c r="AW64" s="136"/>
     </row>
     <row r="65" spans="1:49" s="125" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A65" s="160"/>
-      <c r="B65" s="161"/>
+      <c r="A65" s="186"/>
+      <c r="B65" s="175"/>
       <c r="C65" s="120">
         <f t="shared" si="10"/>
         <v>60</v>
@@ -9392,7 +9392,7 @@
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="K65" s="162"/>
+      <c r="K65" s="176"/>
       <c r="L65" s="124">
         <v>8</v>
       </c>
@@ -9452,8 +9452,8 @@
       <c r="AW65" s="136"/>
     </row>
     <row r="66" spans="1:49" s="125" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A66" s="160"/>
-      <c r="B66" s="161"/>
+      <c r="A66" s="186"/>
+      <c r="B66" s="175"/>
       <c r="C66" s="120">
         <f t="shared" si="10"/>
         <v>62</v>
@@ -9481,7 +9481,7 @@
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="K66" s="162"/>
+      <c r="K66" s="176"/>
       <c r="L66" s="124">
         <v>8</v>
       </c>
@@ -9541,8 +9541,8 @@
       <c r="AW66" s="136"/>
     </row>
     <row r="67" spans="1:49" s="125" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A67" s="160"/>
-      <c r="B67" s="161"/>
+      <c r="A67" s="186"/>
+      <c r="B67" s="175"/>
       <c r="C67" s="120">
         <f t="shared" si="10"/>
         <v>64</v>
@@ -9570,7 +9570,7 @@
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="K67" s="162"/>
+      <c r="K67" s="176"/>
       <c r="L67" s="124">
         <v>6</v>
       </c>
@@ -9630,10 +9630,10 @@
       <c r="AW67" s="136"/>
     </row>
     <row r="68" spans="1:49" s="129" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A68" s="163">
+      <c r="A68" s="187">
         <v>1536</v>
       </c>
-      <c r="B68" s="163">
+      <c r="B68" s="187">
         <v>7071</v>
       </c>
       <c r="C68" s="120">
@@ -9661,7 +9661,7 @@
         <f t="shared" si="0"/>
         <v>300</v>
       </c>
-      <c r="K68" s="163">
+      <c r="K68" s="187">
         <f>SUM(J68:J82)</f>
         <v>1896</v>
       </c>
@@ -9724,8 +9724,8 @@
       <c r="AW68" s="137"/>
     </row>
     <row r="69" spans="1:49" s="129" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A69" s="164"/>
-      <c r="B69" s="164"/>
+      <c r="A69" s="188"/>
+      <c r="B69" s="188"/>
       <c r="C69" s="120">
         <f t="shared" ref="C69:C82" si="12">E68+1</f>
         <v>51</v>
@@ -9753,7 +9753,7 @@
         <f t="shared" si="0"/>
         <v>120</v>
       </c>
-      <c r="K69" s="164"/>
+      <c r="K69" s="188"/>
       <c r="L69" s="124">
         <v>5</v>
       </c>
@@ -9813,8 +9813,8 @@
       <c r="AW69" s="137"/>
     </row>
     <row r="70" spans="1:49" s="129" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A70" s="164"/>
-      <c r="B70" s="164"/>
+      <c r="A70" s="188"/>
+      <c r="B70" s="188"/>
       <c r="C70" s="120">
         <f t="shared" si="12"/>
         <v>71</v>
@@ -9842,7 +9842,7 @@
         <f t="shared" si="0"/>
         <v>120</v>
       </c>
-      <c r="K70" s="164"/>
+      <c r="K70" s="188"/>
       <c r="L70" s="124">
         <v>5</v>
       </c>
@@ -9902,8 +9902,8 @@
       <c r="AW70" s="137"/>
     </row>
     <row r="71" spans="1:49" s="129" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A71" s="164"/>
-      <c r="B71" s="164"/>
+      <c r="A71" s="188"/>
+      <c r="B71" s="188"/>
       <c r="C71" s="120">
         <f t="shared" si="12"/>
         <v>91</v>
@@ -9931,7 +9931,7 @@
         <f t="shared" si="0"/>
         <v>180</v>
       </c>
-      <c r="K71" s="164"/>
+      <c r="K71" s="188"/>
       <c r="L71" s="124">
         <v>5</v>
       </c>
@@ -9991,8 +9991,8 @@
       <c r="AW71" s="137"/>
     </row>
     <row r="72" spans="1:49" s="129" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A72" s="164"/>
-      <c r="B72" s="164"/>
+      <c r="A72" s="188"/>
+      <c r="B72" s="188"/>
       <c r="C72" s="120">
         <f t="shared" si="12"/>
         <v>121</v>
@@ -10020,7 +10020,7 @@
         <f t="shared" si="0"/>
         <v>48</v>
       </c>
-      <c r="K72" s="164"/>
+      <c r="K72" s="188"/>
       <c r="L72" s="124">
         <v>5</v>
       </c>
@@ -10080,8 +10080,8 @@
       <c r="AW72" s="137"/>
     </row>
     <row r="73" spans="1:49" s="129" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A73" s="164"/>
-      <c r="B73" s="164"/>
+      <c r="A73" s="188"/>
+      <c r="B73" s="188"/>
       <c r="C73" s="120">
         <f t="shared" si="12"/>
         <v>129</v>
@@ -10109,7 +10109,7 @@
         <f t="shared" si="0"/>
         <v>60</v>
       </c>
-      <c r="K73" s="164"/>
+      <c r="K73" s="188"/>
       <c r="L73" s="124">
         <v>5</v>
       </c>
@@ -10169,8 +10169,8 @@
       <c r="AW73" s="137"/>
     </row>
     <row r="74" spans="1:49" s="129" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A74" s="164"/>
-      <c r="B74" s="164"/>
+      <c r="A74" s="188"/>
+      <c r="B74" s="188"/>
       <c r="C74" s="120">
         <f t="shared" si="12"/>
         <v>139</v>
@@ -10198,7 +10198,7 @@
         <f t="shared" si="0"/>
         <v>240</v>
       </c>
-      <c r="K74" s="164"/>
+      <c r="K74" s="188"/>
       <c r="L74" s="124">
         <v>5</v>
       </c>
@@ -10258,8 +10258,8 @@
       <c r="AW74" s="137"/>
     </row>
     <row r="75" spans="1:49" s="129" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A75" s="164"/>
-      <c r="B75" s="164"/>
+      <c r="A75" s="188"/>
+      <c r="B75" s="188"/>
       <c r="C75" s="120">
         <f t="shared" si="12"/>
         <v>179</v>
@@ -10287,7 +10287,7 @@
         <f t="shared" si="0"/>
         <v>60</v>
       </c>
-      <c r="K75" s="164"/>
+      <c r="K75" s="188"/>
       <c r="L75" s="124">
         <v>5</v>
       </c>
@@ -10347,8 +10347,8 @@
       <c r="AW75" s="137"/>
     </row>
     <row r="76" spans="1:49" s="129" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A76" s="164"/>
-      <c r="B76" s="164"/>
+      <c r="A76" s="188"/>
+      <c r="B76" s="188"/>
       <c r="C76" s="120">
         <f t="shared" si="12"/>
         <v>189</v>
@@ -10376,7 +10376,7 @@
         <f t="shared" si="0"/>
         <v>90</v>
       </c>
-      <c r="K76" s="164"/>
+      <c r="K76" s="188"/>
       <c r="L76" s="124">
         <v>5</v>
       </c>
@@ -10436,8 +10436,8 @@
       <c r="AW76" s="137"/>
     </row>
     <row r="77" spans="1:49" s="129" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A77" s="164"/>
-      <c r="B77" s="164"/>
+      <c r="A77" s="188"/>
+      <c r="B77" s="188"/>
       <c r="C77" s="120">
         <f t="shared" si="12"/>
         <v>204</v>
@@ -10465,7 +10465,7 @@
         <f t="shared" ref="J77:J82" si="14">H77*I77</f>
         <v>240</v>
       </c>
-      <c r="K77" s="164"/>
+      <c r="K77" s="188"/>
       <c r="L77" s="124">
         <v>5</v>
       </c>
@@ -10525,8 +10525,8 @@
       <c r="AW77" s="137"/>
     </row>
     <row r="78" spans="1:49" s="129" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A78" s="164"/>
-      <c r="B78" s="164"/>
+      <c r="A78" s="188"/>
+      <c r="B78" s="188"/>
       <c r="C78" s="120">
         <f t="shared" si="12"/>
         <v>244</v>
@@ -10554,7 +10554,7 @@
         <f t="shared" si="14"/>
         <v>60</v>
       </c>
-      <c r="K78" s="164"/>
+      <c r="K78" s="188"/>
       <c r="L78" s="124">
         <v>5</v>
       </c>
@@ -10614,8 +10614,8 @@
       <c r="AW78" s="137"/>
     </row>
     <row r="79" spans="1:49" s="129" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A79" s="164"/>
-      <c r="B79" s="164"/>
+      <c r="A79" s="188"/>
+      <c r="B79" s="188"/>
       <c r="C79" s="120">
         <f t="shared" si="12"/>
         <v>254</v>
@@ -10643,7 +10643,7 @@
         <f t="shared" si="14"/>
         <v>90</v>
       </c>
-      <c r="K79" s="164"/>
+      <c r="K79" s="188"/>
       <c r="L79" s="124">
         <v>5</v>
       </c>
@@ -10703,8 +10703,8 @@
       <c r="AW79" s="137"/>
     </row>
     <row r="80" spans="1:49" s="129" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A80" s="164"/>
-      <c r="B80" s="164"/>
+      <c r="A80" s="188"/>
+      <c r="B80" s="188"/>
       <c r="C80" s="120">
         <f t="shared" si="12"/>
         <v>269</v>
@@ -10732,7 +10732,7 @@
         <f t="shared" si="14"/>
         <v>180</v>
       </c>
-      <c r="K80" s="164"/>
+      <c r="K80" s="188"/>
       <c r="L80" s="124">
         <v>5</v>
       </c>
@@ -10792,8 +10792,8 @@
       <c r="AW80" s="137"/>
     </row>
     <row r="81" spans="1:49" s="129" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A81" s="164"/>
-      <c r="B81" s="164"/>
+      <c r="A81" s="188"/>
+      <c r="B81" s="188"/>
       <c r="C81" s="120">
         <f t="shared" si="12"/>
         <v>299</v>
@@ -10821,7 +10821,7 @@
         <f t="shared" si="14"/>
         <v>48</v>
       </c>
-      <c r="K81" s="164"/>
+      <c r="K81" s="188"/>
       <c r="L81" s="124">
         <v>5</v>
       </c>
@@ -10881,8 +10881,8 @@
       <c r="AW81" s="137"/>
     </row>
     <row r="82" spans="1:49" s="129" customFormat="1" ht="16.2" customHeight="1">
-      <c r="A82" s="165"/>
-      <c r="B82" s="165"/>
+      <c r="A82" s="189"/>
+      <c r="B82" s="189"/>
       <c r="C82" s="120">
         <f t="shared" si="12"/>
         <v>307</v>
@@ -10910,7 +10910,7 @@
         <f t="shared" si="14"/>
         <v>60</v>
       </c>
-      <c r="K82" s="165"/>
+      <c r="K82" s="189"/>
       <c r="L82" s="124">
         <v>5</v>
       </c>
@@ -11040,6 +11040,30 @@
     </row>
   </sheetData>
   <mergeCells count="40">
+    <mergeCell ref="A31:A67"/>
+    <mergeCell ref="B31:B67"/>
+    <mergeCell ref="K31:K67"/>
+    <mergeCell ref="A68:A82"/>
+    <mergeCell ref="B68:B82"/>
+    <mergeCell ref="K68:K82"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="B28:B30"/>
+    <mergeCell ref="K28:K30"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="B22:B24"/>
+    <mergeCell ref="K22:K24"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="B10:B12"/>
+    <mergeCell ref="K10:K12"/>
+    <mergeCell ref="B25:B27"/>
+    <mergeCell ref="K25:K27"/>
+    <mergeCell ref="A13:A16"/>
+    <mergeCell ref="B13:B16"/>
+    <mergeCell ref="K13:K16"/>
+    <mergeCell ref="A17:A21"/>
+    <mergeCell ref="B17:B21"/>
+    <mergeCell ref="K17:K21"/>
+    <mergeCell ref="A25:A27"/>
     <mergeCell ref="A1:S1"/>
     <mergeCell ref="O2:P2"/>
     <mergeCell ref="B6:F6"/>
@@ -11056,30 +11080,6 @@
     <mergeCell ref="P8:R8"/>
     <mergeCell ref="L9:M9"/>
     <mergeCell ref="N9:O9"/>
-    <mergeCell ref="A10:A12"/>
-    <mergeCell ref="B10:B12"/>
-    <mergeCell ref="K10:K12"/>
-    <mergeCell ref="B25:B27"/>
-    <mergeCell ref="K25:K27"/>
-    <mergeCell ref="A13:A16"/>
-    <mergeCell ref="B13:B16"/>
-    <mergeCell ref="K13:K16"/>
-    <mergeCell ref="A17:A21"/>
-    <mergeCell ref="B17:B21"/>
-    <mergeCell ref="K17:K21"/>
-    <mergeCell ref="A25:A27"/>
-    <mergeCell ref="A28:A30"/>
-    <mergeCell ref="B28:B30"/>
-    <mergeCell ref="K28:K30"/>
-    <mergeCell ref="A22:A24"/>
-    <mergeCell ref="B22:B24"/>
-    <mergeCell ref="K22:K24"/>
-    <mergeCell ref="A31:A67"/>
-    <mergeCell ref="B31:B67"/>
-    <mergeCell ref="K31:K67"/>
-    <mergeCell ref="A68:A82"/>
-    <mergeCell ref="B68:B82"/>
-    <mergeCell ref="K68:K82"/>
   </mergeCells>
   <phoneticPr fontId="12" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
